--- a/data/model_data/twfe_BEN_per_trab.xlsx
+++ b/data/model_data/twfe_BEN_per_trab.xlsx
@@ -388,16 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.649378213654724</v>
+        <v>2.654557613568233</v>
       </c>
       <c r="C2">
-        <v>0.5305380294189409</v>
+        <v>0.5347320165589311</v>
       </c>
       <c r="D2">
-        <v>4.993757406149362</v>
+        <v>4.96427655604138</v>
       </c>
       <c r="E2">
-        <v>6.468374609401778E-07</v>
+        <v>7.517585927723698E-07</v>
       </c>
     </row>
     <row r="3">
@@ -407,16 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.634231548616227</v>
+        <v>-0.6338218988647909</v>
       </c>
       <c r="C3">
-        <v>0.1428527764418695</v>
+        <v>0.1439820502621935</v>
       </c>
       <c r="D3">
-        <v>-4.439756541058985</v>
+        <v>-4.402089689031317</v>
       </c>
       <c r="E3">
-        <v>9.528049413556217E-06</v>
+        <v>1.132234181589064E-05</v>
       </c>
     </row>
     <row r="4">
@@ -426,16 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>-1.203164705813898</v>
+        <v>-1.215651343039837</v>
       </c>
       <c r="C4">
-        <v>0.7375705844415353</v>
+        <v>0.7434011967152131</v>
       </c>
       <c r="D4">
-        <v>-1.631253647032163</v>
+        <v>-1.63525610183479</v>
       </c>
       <c r="E4">
-        <v>0.1030040337480699</v>
+        <v>0.1021625090011443</v>
       </c>
     </row>
     <row r="5">
@@ -445,16 +445,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>-2.092212346791647</v>
+        <v>-2.090802065350316</v>
       </c>
       <c r="C5">
-        <v>0.7375705844415356</v>
+        <v>0.7434011967152133</v>
       </c>
       <c r="D5">
-        <v>-2.8366266102868</v>
+        <v>-2.812481436119174</v>
       </c>
       <c r="E5">
-        <v>0.004608062386430643</v>
+        <v>0.004967070215802218</v>
       </c>
     </row>
     <row r="6">
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>-2.189723260203824</v>
+        <v>-2.182330290770732</v>
       </c>
       <c r="C6">
-        <v>0.7375705844414716</v>
+        <v>0.7434011967151488</v>
       </c>
       <c r="D6">
-        <v>-2.96883214487465</v>
+        <v>-2.935602337491181</v>
       </c>
       <c r="E6">
-        <v>0.003027092319667384</v>
+        <v>0.003369356406266039</v>
       </c>
     </row>
     <row r="7">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>-2.913567887450899</v>
+        <v>-2.915956593190231</v>
       </c>
       <c r="C7">
-        <v>0.7401279791382612</v>
+        <v>0.7459788080220126</v>
       </c>
       <c r="D7">
-        <v>-3.936573092187647</v>
+        <v>-3.908900040903288</v>
       </c>
       <c r="E7">
-        <v>8.565928242465114E-05</v>
+        <v>9.599917277697278E-05</v>
       </c>
     </row>
     <row r="8">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3852687592541732</v>
+        <v>-0.373029161470311</v>
       </c>
       <c r="C8">
-        <v>0.7401279791381616</v>
+        <v>0.7459788080219122</v>
       </c>
       <c r="D8">
-        <v>-0.520543433181377</v>
+        <v>-0.5000532956954371</v>
       </c>
       <c r="E8">
-        <v>0.6027460628857422</v>
+        <v>0.6170959814391719</v>
       </c>
     </row>
     <row r="9">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.031988164986542</v>
+        <v>-1.03883598436082</v>
       </c>
       <c r="C9">
-        <v>0.7375705844414838</v>
+        <v>0.7434011967151611</v>
       </c>
       <c r="D9">
-        <v>-1.399172074857083</v>
+        <v>-1.397409620741916</v>
       </c>
       <c r="E9">
-        <v>0.1619260876420898</v>
+        <v>0.1624550504644619</v>
       </c>
     </row>
     <row r="10">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>2.740221941775686</v>
+        <v>2.74277495373404</v>
       </c>
       <c r="C10">
-        <v>0.7401279791382198</v>
+        <v>0.7459788080219708</v>
       </c>
       <c r="D10">
-        <v>3.70236231977922</v>
+        <v>3.676746476225983</v>
       </c>
       <c r="E10">
-        <v>0.000219747930740986</v>
+        <v>0.000242848565086909</v>
       </c>
     </row>
     <row r="11">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.353341072666691</v>
+        <v>-1.325918415641538</v>
       </c>
       <c r="C11">
-        <v>0.740127979138263</v>
+        <v>0.7459788080220143</v>
       </c>
       <c r="D11">
-        <v>-1.828523053867517</v>
+        <v>-1.777421022397742</v>
       </c>
       <c r="E11">
-        <v>0.06762920279260852</v>
+        <v>0.07566036679459824</v>
       </c>
     </row>
     <row r="12">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>-2.20408527836226</v>
+        <v>-2.199370135213894</v>
       </c>
       <c r="C12">
-        <v>0.7401279791382389</v>
+        <v>0.7459788080219901</v>
       </c>
       <c r="D12">
-        <v>-2.977978593551571</v>
+        <v>-2.948301093224971</v>
       </c>
       <c r="E12">
-        <v>0.002938622847630467</v>
+        <v>0.003234600023255005</v>
       </c>
     </row>
     <row r="13">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>-2.189782950995415</v>
+        <v>-2.183081416355031</v>
       </c>
       <c r="C13">
-        <v>0.7401279791382666</v>
+        <v>0.7459788080220179</v>
       </c>
       <c r="D13">
-        <v>-2.958654466143797</v>
+        <v>-2.926465729158617</v>
       </c>
       <c r="E13">
-        <v>0.003128389558030589</v>
+        <v>0.003469455382080241</v>
       </c>
     </row>
     <row r="14">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.1622564389710343</v>
+        <v>0.1887867881092749</v>
       </c>
       <c r="C14">
-        <v>0.7373997761065841</v>
+        <v>0.7432290381133244</v>
       </c>
       <c r="D14">
-        <v>0.2200386333553506</v>
+        <v>0.2540088968920096</v>
       </c>
       <c r="E14">
-        <v>0.8258649185785316</v>
+        <v>0.7995164174398804</v>
       </c>
     </row>
     <row r="15">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.6259014363041248</v>
+        <v>-0.5817455698762448</v>
       </c>
       <c r="C15">
-        <v>0.740127979138284</v>
+        <v>0.7459788080220354</v>
       </c>
       <c r="D15">
-        <v>-0.8456664981546153</v>
+        <v>-0.7798419521041684</v>
       </c>
       <c r="E15">
-        <v>0.3978462627664474</v>
+        <v>0.435581916564343</v>
       </c>
     </row>
     <row r="16">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>-1.727994579049936</v>
+        <v>-1.710678319439734</v>
       </c>
       <c r="C16">
-        <v>0.7373997761065598</v>
+        <v>0.7432290381133</v>
       </c>
       <c r="D16">
-        <v>-2.343361952418368</v>
+        <v>-2.301683911304544</v>
       </c>
       <c r="E16">
-        <v>0.01921438314596274</v>
+        <v>0.02146169788963038</v>
       </c>
     </row>
     <row r="17">
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.8816299728023657</v>
+        <v>0.9037394961161932</v>
       </c>
       <c r="C17">
-        <v>0.7373997761066828</v>
+        <v>0.7432290381134239</v>
       </c>
       <c r="D17">
-        <v>1.195592948857658</v>
+        <v>1.215963652887138</v>
       </c>
       <c r="E17">
-        <v>0.2320059865880817</v>
+        <v>0.2241511813683015</v>
       </c>
     </row>
     <row r="18">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>-2.477175161726222</v>
+        <v>-2.442476942530486</v>
       </c>
       <c r="C18">
-        <v>0.7401279791381911</v>
+        <v>0.7459788080219417</v>
       </c>
       <c r="D18">
-        <v>-3.346955163903759</v>
+        <v>-3.274190789691501</v>
       </c>
       <c r="E18">
-        <v>0.0008331205127304969</v>
+        <v>0.001078859372188851</v>
       </c>
     </row>
     <row r="19">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.1350524882819883</v>
+        <v>-0.1197897680844495</v>
       </c>
       <c r="C19">
-        <v>0.7373997761066374</v>
+        <v>0.7432290381133781</v>
       </c>
       <c r="D19">
-        <v>-0.183146907088914</v>
+        <v>-0.1611747683978082</v>
       </c>
       <c r="E19">
-        <v>0.8547024688007666</v>
+        <v>0.8719730431591699</v>
       </c>
     </row>
     <row r="20">
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.188393516197177</v>
+        <v>-1.167299293436973</v>
       </c>
       <c r="C20">
-        <v>0.7373997761065973</v>
+        <v>0.7432290381133377</v>
       </c>
       <c r="D20">
-        <v>-1.611600050208565</v>
+        <v>-1.570578157710474</v>
       </c>
       <c r="E20">
-        <v>0.107216587812666</v>
+        <v>0.1164486752682434</v>
       </c>
     </row>
     <row r="21">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.5128790962088166</v>
+        <v>-0.4829066762319748</v>
       </c>
       <c r="C21">
-        <v>0.7401279791382849</v>
+        <v>0.7459788080220364</v>
       </c>
       <c r="D21">
-        <v>-0.6929600159231255</v>
+        <v>-0.6473463737024948</v>
       </c>
       <c r="E21">
-        <v>0.4884200998254603</v>
+        <v>0.5174867038772591</v>
       </c>
     </row>
     <row r="22">
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.389856669181482</v>
+        <v>-1.353892858806702</v>
       </c>
       <c r="C22">
-        <v>0.7373997761066107</v>
+        <v>0.7432290381133512</v>
       </c>
       <c r="D22">
-        <v>-1.884807555163323</v>
+        <v>-1.821636116698952</v>
       </c>
       <c r="E22">
-        <v>0.05960970545604038</v>
+        <v>0.06866880361131185</v>
       </c>
     </row>
     <row r="23">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.834726265486031</v>
+        <v>-1.849025217488757</v>
       </c>
       <c r="C23">
-        <v>0.7401279791383105</v>
+        <v>0.7459788080220622</v>
       </c>
       <c r="D23">
-        <v>-2.478931100026916</v>
+        <v>-2.478656494802292</v>
       </c>
       <c r="E23">
-        <v>0.01326466110817863</v>
+        <v>0.01327484262259148</v>
       </c>
     </row>
     <row r="24">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.431353974934645</v>
+        <v>-1.446323647228305</v>
       </c>
       <c r="C24">
-        <v>0.7401279791382815</v>
+        <v>0.745978808022033</v>
       </c>
       <c r="D24">
-        <v>-1.933927665592572</v>
+        <v>-1.938826722254001</v>
       </c>
       <c r="E24">
-        <v>0.05327170888538615</v>
+        <v>0.05267168604121748</v>
       </c>
     </row>
     <row r="25">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.4016032534171545</v>
+        <v>-0.36465534157425</v>
       </c>
       <c r="C25">
-        <v>0.740127979138217</v>
+        <v>0.745978808021968</v>
       </c>
       <c r="D25">
-        <v>-0.5426132570812542</v>
+        <v>-0.4888280171673609</v>
       </c>
       <c r="E25">
-        <v>0.5874603228750486</v>
+        <v>0.6250203877402828</v>
       </c>
     </row>
     <row r="26">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>3.485569448630398</v>
+        <v>3.543602312185214</v>
       </c>
       <c r="C26">
-        <v>0.740127979138214</v>
+        <v>0.7459788080219649</v>
       </c>
       <c r="D26">
-        <v>4.709414515971826</v>
+        <v>4.750272090947756</v>
       </c>
       <c r="E26">
-        <v>2.66590728449141E-06</v>
+        <v>2.185110984911704E-06</v>
       </c>
     </row>
     <row r="27">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.682598352981529</v>
+        <v>-1.655709813711397</v>
       </c>
       <c r="C27">
-        <v>0.7373997761066685</v>
+        <v>0.7432290381134096</v>
       </c>
       <c r="D27">
-        <v>-2.28179938142283</v>
+        <v>-2.227724871883641</v>
       </c>
       <c r="E27">
-        <v>0.02261232907289732</v>
+        <v>0.02601661635479327</v>
       </c>
     </row>
     <row r="28">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.3848048982739641</v>
+        <v>-0.3809965727020956</v>
       </c>
       <c r="C28">
-        <v>0.7373997761066877</v>
+        <v>0.7432290381134288</v>
       </c>
       <c r="D28">
-        <v>-0.5218402700169659</v>
+        <v>-0.5126233679851855</v>
       </c>
       <c r="E28">
-        <v>0.6018429239493106</v>
+        <v>0.6082749292458927</v>
       </c>
     </row>
     <row r="29">
@@ -901,16 +901,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>2.760128468957023</v>
+        <v>2.771208015435339</v>
       </c>
       <c r="C29">
-        <v>0.7401279791382147</v>
+        <v>0.7459788080219657</v>
       </c>
       <c r="D29">
-        <v>3.729258380653091</v>
+        <v>3.714861582708312</v>
       </c>
       <c r="E29">
-        <v>0.0001977245761417163</v>
+        <v>0.0002092409890067919</v>
       </c>
     </row>
     <row r="30">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.553801212609904</v>
+        <v>-1.532626968719912</v>
       </c>
       <c r="C30">
-        <v>0.7373997761066355</v>
+        <v>0.7432290381133763</v>
       </c>
       <c r="D30">
-        <v>-2.107135454819026</v>
+        <v>-2.062119333510374</v>
       </c>
       <c r="E30">
-        <v>0.0352377747921051</v>
+        <v>0.0393332935651628</v>
       </c>
     </row>
     <row r="31">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.9407469698922152</v>
+        <v>0.9879764799605779</v>
       </c>
       <c r="C31">
-        <v>0.7401279791382254</v>
+        <v>0.7459788080219765</v>
       </c>
       <c r="D31">
-        <v>1.271059865872903</v>
+        <v>1.32440287758345</v>
       </c>
       <c r="E31">
-        <v>0.2038643458063341</v>
+        <v>0.1855300013957146</v>
       </c>
     </row>
     <row r="32">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.671198750978401</v>
+        <v>-1.642522280594455</v>
       </c>
       <c r="C32">
-        <v>0.7375705844416059</v>
+        <v>0.7434011967152843</v>
       </c>
       <c r="D32">
-        <v>-2.26581534870133</v>
+        <v>-2.209469513705297</v>
       </c>
       <c r="E32">
-        <v>0.02357579508860845</v>
+        <v>0.0272619553747051</v>
       </c>
     </row>
     <row r="33">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.5685393679128765</v>
+        <v>-0.532809711639284</v>
       </c>
       <c r="C33">
-        <v>0.7375705844414414</v>
+        <v>0.7434011967151185</v>
       </c>
       <c r="D33">
-        <v>-0.7708270637493341</v>
+        <v>-0.7167189318414078</v>
       </c>
       <c r="E33">
-        <v>0.4409061490902989</v>
+        <v>0.4736364260966043</v>
       </c>
     </row>
     <row r="34">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.2106850525326477</v>
+        <v>0.2575520199359997</v>
       </c>
       <c r="C34">
-        <v>0.7401279791382001</v>
+        <v>0.7459788080219509</v>
       </c>
       <c r="D34">
-        <v>0.284660299936192</v>
+        <v>0.3452538023418234</v>
       </c>
       <c r="E34">
-        <v>0.7759357105584604</v>
+        <v>0.7299421361599021</v>
       </c>
     </row>
     <row r="35">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.01550582763449949</v>
+        <v>0.05330283479380211</v>
       </c>
       <c r="C35">
-        <v>0.7401279791382517</v>
+        <v>0.745978808022003</v>
       </c>
       <c r="D35">
-        <v>-0.02095019790030542</v>
+        <v>0.07145355098643756</v>
       </c>
       <c r="E35">
-        <v>0.9832876029117233</v>
+        <v>0.9430443789659567</v>
       </c>
     </row>
     <row r="36">
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>3.317191791123333</v>
+        <v>3.306884783302329</v>
       </c>
       <c r="C36">
-        <v>0.7401279791383019</v>
+        <v>0.7459788080220534</v>
       </c>
       <c r="D36">
-        <v>4.481916485558879</v>
+        <v>4.432947354188871</v>
       </c>
       <c r="E36">
-        <v>7.842500447819297E-06</v>
+        <v>9.830875321395096E-06</v>
       </c>
     </row>
     <row r="37">
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="B37">
-        <v>-2.583386642313978</v>
+        <v>-2.565612427114132</v>
       </c>
       <c r="C37">
-        <v>0.7401279791382045</v>
+        <v>0.7459788080219553</v>
       </c>
       <c r="D37">
-        <v>-3.49045937342085</v>
+        <v>-3.439256450082188</v>
       </c>
       <c r="E37">
-        <v>0.0004932956916963465</v>
+        <v>0.0005960224572638517</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.911168487288589</v>
+        <v>1.915999671406122</v>
       </c>
       <c r="C38">
-        <v>0.7375705844414751</v>
+        <v>0.7434011967151524</v>
       </c>
       <c r="D38">
-        <v>2.591166903349081</v>
+        <v>2.577342732124055</v>
       </c>
       <c r="E38">
-        <v>0.009638992155759909</v>
+        <v>0.01003177055471558</v>
       </c>
     </row>
     <row r="39">
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>3.733111735391712</v>
+        <v>3.746636213316461</v>
       </c>
       <c r="C39">
-        <v>0.740127979138213</v>
+        <v>0.745978808021964</v>
       </c>
       <c r="D39">
-        <v>5.043873276806068</v>
+        <v>5.02244322898533</v>
       </c>
       <c r="E39">
-        <v>5.00050029339493E-07</v>
+        <v>5.583882558415761E-07</v>
       </c>
     </row>
     <row r="40">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.505151123374725</v>
+        <v>1.499038472747005</v>
       </c>
       <c r="C40">
-        <v>0.7373997761065355</v>
+        <v>0.7432290381132753</v>
       </c>
       <c r="D40">
-        <v>2.041160266310237</v>
+        <v>2.016926675190719</v>
       </c>
       <c r="E40">
-        <v>0.04137405961804743</v>
+        <v>0.04384484997244502</v>
       </c>
     </row>
     <row r="41">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B41">
-        <v>-1.499227122100608</v>
+        <v>-1.483514134697903</v>
       </c>
       <c r="C41">
-        <v>0.7373997761066171</v>
+        <v>0.7432290381133576</v>
       </c>
       <c r="D41">
-        <v>-2.033126630464073</v>
+        <v>-1.996038984784172</v>
       </c>
       <c r="E41">
-        <v>0.04217973630944671</v>
+        <v>0.04607347561011672</v>
       </c>
     </row>
     <row r="42">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="B42">
-        <v>-2.626482047957711</v>
+        <v>-2.617836586483584</v>
       </c>
       <c r="C42">
-        <v>0.737399776106575</v>
+        <v>0.7432290381133153</v>
       </c>
       <c r="D42">
-        <v>-3.561815629813957</v>
+        <v>-3.522247452991011</v>
       </c>
       <c r="E42">
-        <v>0.0003774528859912946</v>
+        <v>0.0004381012107157875</v>
       </c>
     </row>
     <row r="43">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.160425471485292</v>
+        <v>-1.153773955189712</v>
       </c>
       <c r="C43">
-        <v>0.7373997761066368</v>
+        <v>0.7432290381133775</v>
       </c>
       <c r="D43">
-        <v>-1.573672123433735</v>
+        <v>-1.552380082078692</v>
       </c>
       <c r="E43">
-        <v>0.1157312626473186</v>
+        <v>0.1207393527807463</v>
       </c>
     </row>
     <row r="44">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.7816061447256046</v>
+        <v>-0.778332203115346</v>
       </c>
       <c r="C44">
-        <v>0.737399776106662</v>
+        <v>0.7432290381134029</v>
       </c>
       <c r="D44">
-        <v>-1.059948985680935</v>
+        <v>-1.047230615600069</v>
       </c>
       <c r="E44">
-        <v>0.2893037468544195</v>
+        <v>0.2951276295594592</v>
       </c>
     </row>
     <row r="45">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>-1.167337994346141</v>
+        <v>-1.168386238645545</v>
       </c>
       <c r="C45">
-        <v>0.7373997761066716</v>
+        <v>0.7432290381134126</v>
       </c>
       <c r="D45">
-        <v>-1.583046309709315</v>
+        <v>-1.572040621032969</v>
       </c>
       <c r="E45">
-        <v>0.1135788392191444</v>
+        <v>0.1161091323416572</v>
       </c>
     </row>
     <row r="46">
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.419039949971236</v>
+        <v>-1.402253328973953</v>
       </c>
       <c r="C46">
-        <v>0.7373997761066277</v>
+        <v>0.7432290381133683</v>
       </c>
       <c r="D46">
-        <v>-1.924383483628891</v>
+        <v>-1.886704174709681</v>
       </c>
       <c r="E46">
-        <v>0.0544570689281828</v>
+        <v>0.05935385310762323</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.339150131731202</v>
+        <v>-1.327327458893511</v>
       </c>
       <c r="C47">
-        <v>0.7375705844415691</v>
+        <v>0.7434011967152472</v>
       </c>
       <c r="D47">
-        <v>-1.815623019653234</v>
+        <v>-1.785479314209298</v>
       </c>
       <c r="E47">
-        <v>0.06958721092176483</v>
+        <v>0.07434450121266069</v>
       </c>
     </row>
     <row r="48">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.483067970199315</v>
+        <v>-1.47412292825257</v>
       </c>
       <c r="C48">
-        <v>0.7373997761066029</v>
+        <v>0.7432290381133434</v>
       </c>
       <c r="D48">
-        <v>-2.011212938020901</v>
+        <v>-1.983403301887358</v>
       </c>
       <c r="E48">
-        <v>0.04444523766076173</v>
+        <v>0.04746744182392898</v>
       </c>
     </row>
     <row r="49">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B49">
-        <v>-3.048797221639419</v>
+        <v>-3.041472493125888</v>
       </c>
       <c r="C49">
-        <v>0.7401279791382137</v>
+        <v>0.7459788080219646</v>
       </c>
       <c r="D49">
-        <v>-4.119283836816116</v>
+        <v>-4.077156697240031</v>
       </c>
       <c r="E49">
-        <v>3.96510737597811E-05</v>
+        <v>4.748730560511028E-05</v>
       </c>
     </row>
     <row r="50">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="B50">
-        <v>-2.670556791090189</v>
+        <v>-2.664942805459189</v>
       </c>
       <c r="C50">
-        <v>0.7373997761065959</v>
+        <v>0.7432290381133363</v>
       </c>
       <c r="D50">
-        <v>-3.6215861160014</v>
+        <v>-3.585627940781301</v>
       </c>
       <c r="E50">
-        <v>0.0003005521379053158</v>
+        <v>0.000344838826189664</v>
       </c>
     </row>
     <row r="51">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.1960521192071975</v>
+        <v>-0.1681134079124702</v>
       </c>
       <c r="C51">
-        <v>0.7373997761066317</v>
+        <v>0.7432290381133724</v>
       </c>
       <c r="D51">
-        <v>-0.2658695127930815</v>
+        <v>-0.22619327191415</v>
       </c>
       <c r="E51">
-        <v>0.7903688114383619</v>
+        <v>0.8210756525898569</v>
       </c>
     </row>
     <row r="52">
@@ -1338,16 +1338,16 @@
         </is>
       </c>
       <c r="B52">
-        <v>-1.572298830915434</v>
+        <v>-1.549336523458007</v>
       </c>
       <c r="C52">
-        <v>0.7373997761066633</v>
+        <v>0.7432290381134042</v>
       </c>
       <c r="D52">
-        <v>-2.13222038012662</v>
+        <v>-2.084601709576375</v>
       </c>
       <c r="E52">
-        <v>0.03311780600539022</v>
+        <v>0.03723992490677967</v>
       </c>
     </row>
     <row r="53">
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.7065395211274726</v>
+        <v>0.7431187017891937</v>
       </c>
       <c r="C53">
-        <v>0.7373997761067004</v>
+        <v>0.7432290381134415</v>
       </c>
       <c r="D53">
-        <v>0.9581498991738746</v>
+        <v>0.9998515446536805</v>
       </c>
       <c r="E53">
-        <v>0.3381101794345249</v>
+        <v>0.3175108235291534</v>
       </c>
     </row>
     <row r="54">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="B54">
-        <v>-2.254590752007247</v>
+        <v>-2.241002595424638</v>
       </c>
       <c r="C54">
-        <v>0.7373997761066576</v>
+        <v>0.7432290381133985</v>
       </c>
       <c r="D54">
-        <v>-3.05748770892106</v>
+        <v>-3.015224756440041</v>
       </c>
       <c r="E54">
-        <v>0.002263411329968744</v>
+        <v>0.002602216527488184</v>
       </c>
     </row>
     <row r="55">
@@ -1395,16 +1395,16 @@
         </is>
       </c>
       <c r="B55">
-        <v>-2.725562453230656</v>
+        <v>-2.724427258127203</v>
       </c>
       <c r="C55">
-        <v>0.7373997761066523</v>
+        <v>0.7432290381133931</v>
       </c>
       <c r="D55">
-        <v>-3.696180201764057</v>
+        <v>-3.665663097667535</v>
       </c>
       <c r="E55">
-        <v>0.0002251260071349945</v>
+        <v>0.0002535342503847564</v>
       </c>
     </row>
     <row r="56">
@@ -1414,16 +1414,16 @@
         </is>
       </c>
       <c r="B56">
-        <v>-3.182145372930156</v>
+        <v>-3.185124013011676</v>
       </c>
       <c r="C56">
-        <v>0.7373997761066151</v>
+        <v>0.7432290381133557</v>
       </c>
       <c r="D56">
-        <v>-4.315359830635578</v>
+        <v>-4.285521487557766</v>
       </c>
       <c r="E56">
-        <v>1.676082553880166E-05</v>
+        <v>1.915154622965578E-05</v>
       </c>
     </row>
     <row r="57">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="B57">
-        <v>-3.22995286483003</v>
+        <v>-3.226265421912622</v>
       </c>
       <c r="C57">
-        <v>0.7373997761065541</v>
+        <v>0.7432290381132941</v>
       </c>
       <c r="D57">
-        <v>-4.380192358999716</v>
+        <v>-4.340876441133919</v>
       </c>
       <c r="E57">
-        <v>1.250934152869602E-05</v>
+        <v>1.494477722931758E-05</v>
       </c>
     </row>
     <row r="58">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="B58">
-        <v>-2.980554876430337</v>
+        <v>-2.974747074142277</v>
       </c>
       <c r="C58">
-        <v>0.7373997761065633</v>
+        <v>0.7432290381133034</v>
       </c>
       <c r="D58">
-        <v>-4.041979633039121</v>
+        <v>-4.002463468991619</v>
       </c>
       <c r="E58">
-        <v>5.513540139583109E-05</v>
+        <v>6.51161153248567E-05</v>
       </c>
     </row>
     <row r="59">
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="B59">
-        <v>-1.025985390118404</v>
+        <v>-1.017146599044242</v>
       </c>
       <c r="C59">
-        <v>0.7373997761065917</v>
+        <v>0.743229038113332</v>
       </c>
       <c r="D59">
-        <v>-1.391355711464302</v>
+        <v>-1.368550671306174</v>
       </c>
       <c r="E59">
-        <v>0.1642819414046356</v>
+        <v>0.1713030237316132</v>
       </c>
     </row>
     <row r="60">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="B60">
-        <v>-3.391744303949537</v>
+        <v>-3.39405873906847</v>
       </c>
       <c r="C60">
-        <v>0.7373997761066274</v>
+        <v>0.7432290381133682</v>
       </c>
       <c r="D60">
-        <v>-4.599600398385656</v>
+        <v>-4.566639037252953</v>
       </c>
       <c r="E60">
-        <v>4.51493315986348E-06</v>
+        <v>5.276909553418431E-06</v>
       </c>
     </row>
     <row r="61">
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="B61">
-        <v>-2.496703614146716</v>
+        <v>-2.496932109370599</v>
       </c>
       <c r="C61">
-        <v>0.7373997761065716</v>
+        <v>0.7432290381133118</v>
       </c>
       <c r="D61">
-        <v>-3.385820954990205</v>
+        <v>-3.359572865598827</v>
       </c>
       <c r="E61">
-        <v>0.0007242360375365446</v>
+        <v>0.0007962079302633453</v>
       </c>
     </row>
     <row r="62">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="B62">
-        <v>-2.814337731260579</v>
+        <v>-2.807808433742073</v>
       </c>
       <c r="C62">
-        <v>0.7373997761065647</v>
+        <v>0.7432290381133049</v>
       </c>
       <c r="D62">
-        <v>-3.816569820674677</v>
+        <v>-3.777850823576169</v>
       </c>
       <c r="E62">
-        <v>0.0001396912444432188</v>
+        <v>0.0001631028858624441</v>
       </c>
     </row>
     <row r="63">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="B63">
-        <v>-2.964221221187721</v>
+        <v>-2.959902849888945</v>
       </c>
       <c r="C63">
-        <v>0.7373997761065951</v>
+        <v>0.7432290381133355</v>
       </c>
       <c r="D63">
-        <v>-4.019829293736085</v>
+        <v>-3.982490858272397</v>
       </c>
       <c r="E63">
-        <v>6.05356778280544E-05</v>
+        <v>7.078975058285637E-05</v>
       </c>
     </row>
     <row r="64">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="B64">
-        <v>-3.290118616990956</v>
+        <v>-3.299332498425819</v>
       </c>
       <c r="C64">
-        <v>0.7373997761066807</v>
+        <v>0.7432290381134218</v>
       </c>
       <c r="D64">
-        <v>-4.46178412795581</v>
+        <v>-4.439186750292605</v>
       </c>
       <c r="E64">
-        <v>8.608318850488655E-06</v>
+        <v>9.553043899516307E-06</v>
       </c>
     </row>
     <row r="65">
@@ -1585,16 +1585,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>-2.5866440413327</v>
+        <v>-2.595104619319332</v>
       </c>
       <c r="C65">
-        <v>0.7373997761067014</v>
+        <v>0.7432290381134427</v>
       </c>
       <c r="D65">
-        <v>-3.507790651889775</v>
+        <v>-3.491662039882824</v>
       </c>
       <c r="E65">
-        <v>0.0004624461418498704</v>
+        <v>0.0004910944300851666</v>
       </c>
     </row>
     <row r="66">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="B66">
-        <v>-2.65015267489478</v>
+        <v>-2.662597869253716</v>
       </c>
       <c r="C66">
-        <v>0.7373997761066509</v>
+        <v>0.7432290381133917</v>
       </c>
       <c r="D66">
-        <v>-3.593915757456761</v>
+        <v>-3.582472875403845</v>
       </c>
       <c r="E66">
-        <v>0.0003341204727148346</v>
+        <v>0.0003490031141240017</v>
       </c>
     </row>
     <row r="67">
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="B67">
-        <v>-1.690373758638233</v>
+        <v>-1.691651714350195</v>
       </c>
       <c r="C67">
-        <v>0.73739977610667</v>
+        <v>0.743229038113411</v>
       </c>
       <c r="D67">
-        <v>-2.292343737291437</v>
+        <v>-2.276083989727083</v>
       </c>
       <c r="E67">
-        <v>0.02199566028621963</v>
+        <v>0.02295282715201876</v>
       </c>
     </row>
     <row r="68">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="B68">
-        <v>-3.444966215866932</v>
+        <v>-3.450851201093694</v>
       </c>
       <c r="C68">
-        <v>0.7373997761066078</v>
+        <v>0.7432290381133483</v>
       </c>
       <c r="D68">
-        <v>-4.671775511047733</v>
+        <v>-4.643052173867583</v>
       </c>
       <c r="E68">
-        <v>3.197545789447888E-06</v>
+        <v>3.67026795181545E-06</v>
       </c>
     </row>
     <row r="69">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="B69">
-        <v>-3.043335246763495</v>
+        <v>-3.030843726382837</v>
       </c>
       <c r="C69">
-        <v>0.7401279791382371</v>
+        <v>0.7459788080219882</v>
       </c>
       <c r="D69">
-        <v>-4.111904065979213</v>
+        <v>-4.06290861588859</v>
       </c>
       <c r="E69">
-        <v>4.092861699688666E-05</v>
+        <v>5.045516306619597E-05</v>
       </c>
     </row>
     <row r="70">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="B70">
-        <v>-1.575477512045748</v>
+        <v>-1.566319149831604</v>
       </c>
       <c r="C70">
-        <v>0.7401279791382688</v>
+        <v>0.7459788080220201</v>
       </c>
       <c r="D70">
-        <v>-2.128655525062134</v>
+        <v>-2.09968317194524</v>
       </c>
       <c r="E70">
-        <v>0.03341225341393458</v>
+        <v>0.0358894950907396</v>
       </c>
     </row>
     <row r="71">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="B71">
-        <v>-2.360878879634866</v>
+        <v>-2.346572775959904</v>
       </c>
       <c r="C71">
-        <v>0.7373997761066076</v>
+        <v>0.7432290381133481</v>
       </c>
       <c r="D71">
-        <v>-3.201626792050379</v>
+        <v>-3.157267350474584</v>
       </c>
       <c r="E71">
-        <v>0.001389332177130715</v>
+        <v>0.00161777747960461</v>
       </c>
     </row>
     <row r="72">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.87832832967831</v>
+        <v>-1.852988733235636</v>
       </c>
       <c r="C72">
-        <v>0.7375705844414935</v>
+        <v>0.7434011967151709</v>
       </c>
       <c r="D72">
-        <v>-2.546642137444549</v>
+        <v>-2.492582392150218</v>
       </c>
       <c r="E72">
-        <v>0.01095547748526644</v>
+        <v>0.01276714298857805</v>
       </c>
     </row>
     <row r="73">
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B73">
-        <v>-3.112486741018615</v>
+        <v>-3.109915194124395</v>
       </c>
       <c r="C73">
-        <v>0.737399776106574</v>
+        <v>0.7432290381133142</v>
       </c>
       <c r="D73">
-        <v>-4.220894610861364</v>
+        <v>-4.184329506310612</v>
       </c>
       <c r="E73">
-        <v>2.549156852192065E-05</v>
+        <v>2.991694126669596E-05</v>
       </c>
     </row>
     <row r="74">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="B74">
-        <v>11.44734970750179</v>
+        <v>11.45435493395321</v>
       </c>
       <c r="C74">
-        <v>0.7375705844414894</v>
+        <v>0.7434011967151667</v>
       </c>
       <c r="D74">
-        <v>15.52034469510476</v>
+        <v>15.40803940667039</v>
       </c>
       <c r="E74">
-        <v>3.264608517139507E-51</v>
+        <v>1.534094465805742E-50</v>
       </c>
     </row>
     <row r="75">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B75">
-        <v>3.260522533943939</v>
+        <v>3.290529161042794</v>
       </c>
       <c r="C75">
-        <v>0.7375705844415759</v>
+        <v>0.7434011967152538</v>
       </c>
       <c r="D75">
-        <v>4.420624415780521</v>
+        <v>4.426316739308628</v>
       </c>
       <c r="E75">
-        <v>1.040245575503739E-05</v>
+        <v>1.013458681580371E-05</v>
       </c>
     </row>
     <row r="76">
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="B76">
-        <v>3.445699913978556</v>
+        <v>3.452751930864058</v>
       </c>
       <c r="C76">
-        <v>0.7375705844414809</v>
+        <v>0.7434011967151583</v>
       </c>
       <c r="D76">
-        <v>4.671688359952402</v>
+        <v>4.644533727038128</v>
       </c>
       <c r="E76">
-        <v>3.198887479190815E-06</v>
+        <v>3.64432619762419E-06</v>
       </c>
     </row>
     <row r="77">
@@ -1813,16 +1813,16 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.6309715770682571</v>
+        <v>-0.5914381235717205</v>
       </c>
       <c r="C77">
-        <v>0.7375705844415293</v>
+        <v>0.743401196715207</v>
       </c>
       <c r="D77">
-        <v>-0.8554728054210752</v>
+        <v>-0.7955840348186812</v>
       </c>
       <c r="E77">
-        <v>0.3923982898819374</v>
+        <v>0.4263741251895454</v>
       </c>
     </row>
     <row r="78">
@@ -1832,16 +1832,16 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.876243191877458</v>
+        <v>1.930261602198973</v>
       </c>
       <c r="C78">
-        <v>0.7375705844415213</v>
+        <v>0.743401196715199</v>
       </c>
       <c r="D78">
-        <v>2.543815102520831</v>
+        <v>2.596527434618143</v>
       </c>
       <c r="E78">
-        <v>0.01104422619485907</v>
+        <v>0.0094904168729892</v>
       </c>
     </row>
     <row r="79">
@@ -1851,16 +1851,16 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.06141527376388396</v>
+        <v>0.09383784889911474</v>
       </c>
       <c r="C79">
-        <v>0.7375705844415481</v>
+        <v>0.743401196715226</v>
       </c>
       <c r="D79">
-        <v>0.08326697818403993</v>
+        <v>0.1262277345177064</v>
       </c>
       <c r="E79">
-        <v>0.9336481071951787</v>
+        <v>0.8995651339704611</v>
       </c>
     </row>
     <row r="80">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.274338339398859</v>
+        <v>0.3353030633471439</v>
       </c>
       <c r="C80">
-        <v>0.7375705844414565</v>
+        <v>0.7434011967151336</v>
       </c>
       <c r="D80">
-        <v>0.371948590664863</v>
+        <v>0.4510391761928113</v>
       </c>
       <c r="E80">
-        <v>0.7099729779375679</v>
+        <v>0.6520132484681429</v>
       </c>
     </row>
     <row r="81">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B81">
-        <v>2.166204104292814</v>
+        <v>2.194106845361717</v>
       </c>
       <c r="C81">
-        <v>0.7375705844415457</v>
+        <v>0.7434011967152235</v>
       </c>
       <c r="D81">
-        <v>2.936944815841542</v>
+        <v>2.951443789782086</v>
       </c>
       <c r="E81">
-        <v>0.003354872287383275</v>
+        <v>0.003202018061547765</v>
       </c>
     </row>
     <row r="82">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.107687973491462</v>
+        <v>-0.05166880040251706</v>
       </c>
       <c r="C82">
-        <v>0.7375705844414741</v>
+        <v>0.7434011967151513</v>
       </c>
       <c r="D82">
-        <v>-0.146003617501922</v>
+        <v>-0.06950325158316226</v>
       </c>
       <c r="E82">
-        <v>0.8839341604023341</v>
+        <v>0.9445964244148968</v>
       </c>
     </row>
     <row r="83">
@@ -1927,16 +1927,16 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.4069895086074657</v>
+        <v>0.4515537834109494</v>
       </c>
       <c r="C83">
-        <v>0.7373997761066394</v>
+        <v>0.7432290381133801</v>
       </c>
       <c r="D83">
-        <v>0.5519251860318015</v>
+        <v>0.6075567022477727</v>
       </c>
       <c r="E83">
-        <v>0.5810651069627901</v>
+        <v>0.5435547846139503</v>
       </c>
     </row>
     <row r="84">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="B84">
-        <v>11.11241421246528</v>
+        <v>11.16862102199194</v>
       </c>
       <c r="C84">
-        <v>0.7401279791382049</v>
+        <v>0.7459788080219557</v>
       </c>
       <c r="D84">
-        <v>15.0141793388279</v>
+        <v>14.9717671626715</v>
       </c>
       <c r="E84">
-        <v>3.257540298594254E-48</v>
+        <v>5.763496369611701E-48</v>
       </c>
     </row>
     <row r="85">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="B85">
-        <v>-1.798192574844752</v>
+        <v>-1.750747323324813</v>
       </c>
       <c r="C85">
-        <v>0.7401279791382167</v>
+        <v>0.7459788080219676</v>
       </c>
       <c r="D85">
-        <v>-2.429569784591194</v>
+        <v>-2.346912947791483</v>
       </c>
       <c r="E85">
-        <v>0.01520971094683157</v>
+        <v>0.01903278861878983</v>
       </c>
     </row>
     <row r="86">
@@ -1984,16 +1984,16 @@
         </is>
       </c>
       <c r="B86">
-        <v>2.834851141817381</v>
+        <v>2.926466197216537</v>
       </c>
       <c r="C86">
-        <v>0.7373997761066448</v>
+        <v>0.7432290381133856</v>
       </c>
       <c r="D86">
-        <v>3.84438839510496</v>
+        <v>3.937502502115749</v>
       </c>
       <c r="E86">
-        <v>0.0001248673733052618</v>
+        <v>8.533100021727025E-05</v>
       </c>
     </row>
     <row r="87">
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="B87">
-        <v>-1.637132291882891</v>
+        <v>-1.570218545096614</v>
       </c>
       <c r="C87">
-        <v>0.7401279791382189</v>
+        <v>0.7459788080219699</v>
       </c>
       <c r="D87">
-        <v>-2.211958388316997</v>
+        <v>-2.104910391838329</v>
       </c>
       <c r="E87">
-        <v>0.02708919519917004</v>
+        <v>0.0354312950470727</v>
       </c>
     </row>
     <row r="88">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="B88">
-        <v>7.506470217585747</v>
+        <v>7.547032704959761</v>
       </c>
       <c r="C88">
-        <v>0.7401279791382345</v>
+        <v>0.7459788080219855</v>
       </c>
       <c r="D88">
-        <v>10.14212464488355</v>
+        <v>10.11695322146113</v>
       </c>
       <c r="E88">
-        <v>1.430775618563082E-23</v>
+        <v>1.826361879552599E-23</v>
       </c>
     </row>
     <row r="89">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="B89">
-        <v>4.488396131204418</v>
+        <v>4.569445422826777</v>
       </c>
       <c r="C89">
-        <v>0.7401279791382549</v>
+        <v>0.7459788080220062</v>
       </c>
       <c r="D89">
-        <v>6.064351379379473</v>
+        <v>6.125435969076456</v>
       </c>
       <c r="E89">
-        <v>1.597022992112223E-09</v>
+        <v>1.09821903466854E-09</v>
       </c>
     </row>
     <row r="90">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B90">
-        <v>12.42983164209184</v>
+        <v>12.57053099427293</v>
       </c>
       <c r="C90">
-        <v>0.7401279791381988</v>
+        <v>0.7459788080219497</v>
       </c>
       <c r="D90">
-        <v>16.7941653233608</v>
+        <v>16.85105643631509</v>
       </c>
       <c r="E90">
-        <v>4.316804494515864E-59</v>
+        <v>1.87308548326979E-59</v>
       </c>
     </row>
     <row r="91">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="B91">
-        <v>8.388136921625014</v>
+        <v>8.394099506828075</v>
       </c>
       <c r="C91">
-        <v>0.7401279791382417</v>
+        <v>0.7459788080219928</v>
       </c>
       <c r="D91">
-        <v>11.33336011886975</v>
+        <v>11.25246376513769</v>
       </c>
       <c r="E91">
-        <v>7.536498533214354E-29</v>
+        <v>1.784932658430227E-28</v>
       </c>
     </row>
     <row r="92">
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="B92">
-        <v>2.424316747881993</v>
+        <v>2.488061751540387</v>
       </c>
       <c r="C92">
-        <v>0.740127979138183</v>
+        <v>0.7459788080219336</v>
       </c>
       <c r="D92">
-        <v>3.275537226284712</v>
+        <v>3.335298167702416</v>
       </c>
       <c r="E92">
-        <v>0.00107375907050678</v>
+        <v>0.0008686284131063238</v>
       </c>
     </row>
     <row r="93">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>6.151793899533798</v>
+        <v>6.154115978249181</v>
       </c>
       <c r="C93">
-        <v>0.740127979138224</v>
+        <v>0.745978808021975</v>
       </c>
       <c r="D93">
-        <v>8.31179751736545</v>
+        <v>8.249719579256324</v>
       </c>
       <c r="E93">
-        <v>1.781421533381095E-16</v>
+        <v>2.945949527266091E-16</v>
       </c>
     </row>
     <row r="94">
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="B94">
-        <v>4.171213384120913</v>
+        <v>4.254556555655965</v>
       </c>
       <c r="C94">
-        <v>0.7401279791382538</v>
+        <v>0.745978808022005</v>
       </c>
       <c r="D94">
-        <v>5.635800161179614</v>
+        <v>5.703320938750398</v>
       </c>
       <c r="E94">
-        <v>2.005747010531617E-08</v>
+        <v>1.361470199581039E-08</v>
       </c>
     </row>
     <row r="95">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B95">
-        <v>23.9981952757516</v>
+        <v>24.09597176225181</v>
       </c>
       <c r="C95">
-        <v>0.7621835921158785</v>
+        <v>0.7682087741130043</v>
       </c>
       <c r="D95">
-        <v>31.4861084966823</v>
+        <v>31.36643653943383</v>
       </c>
       <c r="E95">
-        <v>3.532720581722423E-175</v>
+        <v>4.174218611769546E-174</v>
       </c>
     </row>
     <row r="96">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="B96">
-        <v>5.530033793854071</v>
+        <v>5.540663181568644</v>
       </c>
       <c r="C96">
-        <v>0.7621835921158484</v>
+        <v>0.7682087741129739</v>
       </c>
       <c r="D96">
-        <v>7.255514092743066</v>
+        <v>7.212444544084088</v>
       </c>
       <c r="E96">
-        <v>5.821304330621431E-13</v>
+        <v>7.926792875698126E-13</v>
       </c>
     </row>
     <row r="97">
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="B97">
-        <v>6.257187815494017</v>
+        <v>6.358901015343657</v>
       </c>
       <c r="C97">
-        <v>0.7375705844415543</v>
+        <v>0.7434011967152322</v>
       </c>
       <c r="D97">
-        <v>8.483510524259312</v>
+        <v>8.553794429496328</v>
       </c>
       <c r="E97">
-        <v>4.353159173892448E-17</v>
+        <v>2.427019637611369E-17</v>
       </c>
     </row>
     <row r="98">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B98">
-        <v>6.206756833568477</v>
+        <v>6.299139425972093</v>
       </c>
       <c r="C98">
-        <v>0.7401279791382572</v>
+        <v>0.7459788080220084</v>
       </c>
       <c r="D98">
-        <v>8.386058909426858</v>
+        <v>8.444126506320606</v>
       </c>
       <c r="E98">
-        <v>9.716127781432329E-17</v>
+        <v>6.027819878760525E-17</v>
       </c>
     </row>
     <row r="99">
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B99">
-        <v>6.047180561225439</v>
+        <v>6.129649694092417</v>
       </c>
       <c r="C99">
-        <v>0.7401279791382003</v>
+        <v>0.7459788080219512</v>
       </c>
       <c r="D99">
-        <v>8.170452586141566</v>
+        <v>8.216922020004684</v>
       </c>
       <c r="E99">
-        <v>5.572159302817391E-16</v>
+        <v>3.837480994043567E-16</v>
       </c>
     </row>
     <row r="100">
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="B100">
-        <v>9.272271253210311</v>
+        <v>9.292830795925857</v>
       </c>
       <c r="C100">
-        <v>0.7401279791382558</v>
+        <v>0.745978808022007</v>
       </c>
       <c r="D100">
-        <v>12.52792964806733</v>
+        <v>12.45723162105124</v>
       </c>
       <c r="E100">
-        <v>1.212433057537558E-34</v>
+        <v>2.754917482568125E-34</v>
       </c>
     </row>
     <row r="101">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="B101">
-        <v>2.562681999818677</v>
+        <v>2.574521905908386</v>
       </c>
       <c r="C101">
-        <v>0.7373997761066302</v>
+        <v>0.7432290381133708</v>
       </c>
       <c r="D101">
-        <v>3.475295332132167</v>
+        <v>3.463968405275996</v>
       </c>
       <c r="E101">
-        <v>0.0005218522980402803</v>
+        <v>0.0005441809890679875</v>
       </c>
     </row>
     <row r="102">
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B102">
-        <v>10.82174588398997</v>
+        <v>10.8393575323009</v>
       </c>
       <c r="C102">
-        <v>0.7375705844415253</v>
+        <v>0.743401196715203</v>
       </c>
       <c r="D102">
-        <v>14.6721495030662</v>
+        <v>14.58076416905939</v>
       </c>
       <c r="E102">
-        <v>3.130494972646353E-46</v>
+        <v>1.045437178122887E-45</v>
       </c>
     </row>
     <row r="103">
@@ -2307,16 +2307,16 @@
         </is>
       </c>
       <c r="B103">
-        <v>4.246857813441047</v>
+        <v>4.324201661874508</v>
       </c>
       <c r="C103">
-        <v>0.737570584441486</v>
+        <v>0.7434011967151634</v>
       </c>
       <c r="D103">
-        <v>5.75790019697832</v>
+        <v>5.816780603773148</v>
       </c>
       <c r="E103">
-        <v>9.923296032400068E-09</v>
+        <v>7.033014822767274E-09</v>
       </c>
     </row>
     <row r="104">
@@ -2326,16 +2326,16 @@
         </is>
       </c>
       <c r="B104">
-        <v>4.036538824474015</v>
+        <v>4.080651861287768</v>
       </c>
       <c r="C104">
-        <v>0.7375705844415151</v>
+        <v>0.7434011967151927</v>
       </c>
       <c r="D104">
-        <v>5.472749198004505</v>
+        <v>5.489165042131513</v>
       </c>
       <c r="E104">
-        <v>5.024263983275276E-08</v>
+        <v>4.585694843575824E-08</v>
       </c>
     </row>
     <row r="105">
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.5936237606739967</v>
+        <v>-0.5553063292558618</v>
       </c>
       <c r="C105">
-        <v>0.7375705844415273</v>
+        <v>0.7434011967152051</v>
       </c>
       <c r="D105">
-        <v>-0.804836544726734</v>
+        <v>-0.7469806770685063</v>
       </c>
       <c r="E105">
-        <v>0.4210156169302329</v>
+        <v>0.4551684838993351</v>
       </c>
     </row>
     <row r="106">
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.700535331805168</v>
+        <v>1.735122017661409</v>
       </c>
       <c r="C106">
-        <v>0.7375705844415033</v>
+        <v>0.7434011967151808</v>
       </c>
       <c r="D106">
-        <v>2.305589956645075</v>
+        <v>2.334031778975178</v>
       </c>
       <c r="E106">
-        <v>0.02124176718118009</v>
+        <v>0.01969876002137674</v>
       </c>
     </row>
     <row r="107">
@@ -2383,16 +2383,16 @@
         </is>
       </c>
       <c r="B107">
-        <v>2.981351010310607</v>
+        <v>3.061845408889648</v>
       </c>
       <c r="C107">
-        <v>0.7375705844415507</v>
+        <v>0.7434011967152285</v>
       </c>
       <c r="D107">
-        <v>4.042122982125064</v>
+        <v>4.118698520285724</v>
       </c>
       <c r="E107">
-        <v>5.510198851210129E-05</v>
+        <v>3.975100114568386E-05</v>
       </c>
     </row>
     <row r="108">
@@ -2402,16 +2402,16 @@
         </is>
       </c>
       <c r="B108">
-        <v>3.496176740434551</v>
+        <v>3.592690841732417</v>
       </c>
       <c r="C108">
-        <v>0.7401279791382334</v>
+        <v>0.7459788080219846</v>
       </c>
       <c r="D108">
-        <v>4.723746215492782</v>
+        <v>4.816076278706483</v>
       </c>
       <c r="E108">
-        <v>2.486709060593128E-06</v>
+        <v>1.581067067952734E-06</v>
       </c>
     </row>
     <row r="109">
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="B109">
-        <v>3.243674611718321</v>
+        <v>3.393444272414083</v>
       </c>
       <c r="C109">
-        <v>0.7375705844414651</v>
+        <v>0.7434011967151423</v>
       </c>
       <c r="D109">
-        <v>4.397781961674402</v>
+        <v>4.564754922925405</v>
       </c>
       <c r="E109">
-        <v>1.154700443614992E-05</v>
+        <v>5.323997542743963E-06</v>
       </c>
     </row>
     <row r="110">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="B110">
-        <v>6.247208545848865</v>
+        <v>6.393556758955283</v>
       </c>
       <c r="C110">
-        <v>0.7401279791382288</v>
+        <v>0.7459788080219798</v>
       </c>
       <c r="D110">
-        <v>8.440713933180623</v>
+        <v>8.570694891331151</v>
       </c>
       <c r="E110">
-        <v>6.199842547013342E-17</v>
+        <v>2.107561349692899E-17</v>
       </c>
     </row>
     <row r="111">
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B111">
-        <v>2.97599297381975</v>
+        <v>3.080323480507535</v>
       </c>
       <c r="C111">
-        <v>0.7375705844415384</v>
+        <v>0.7434011967152161</v>
       </c>
       <c r="D111">
-        <v>4.034858543163111</v>
+        <v>4.143554643331511</v>
       </c>
       <c r="E111">
-        <v>5.681963056682072E-05</v>
+        <v>3.57113253403068E-05</v>
       </c>
     </row>
     <row r="112">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="B112">
-        <v>3.101881016124544</v>
+        <v>3.209899417746659</v>
       </c>
       <c r="C112">
-        <v>0.7375705844415279</v>
+        <v>0.7434011967152055</v>
       </c>
       <c r="D112">
-        <v>4.205537858418282</v>
+        <v>4.317856134655054</v>
       </c>
       <c r="E112">
-        <v>2.726840700157607E-05</v>
+        <v>1.657427160952949E-05</v>
       </c>
     </row>
     <row r="113">
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="B113">
-        <v>4.797580712175545</v>
+        <v>4.812488137830663</v>
       </c>
       <c r="C113">
-        <v>0.7373997761066385</v>
+        <v>0.7432290381133793</v>
       </c>
       <c r="D113">
-        <v>6.50607834125752</v>
+        <v>6.475107794559178</v>
       </c>
       <c r="E113">
-        <v>9.859088322620483E-11</v>
+        <v>1.205495594038418E-10</v>
       </c>
     </row>
     <row r="114">
@@ -2516,16 +2516,16 @@
         </is>
       </c>
       <c r="B114">
-        <v>3.103815738343208</v>
+        <v>3.187568445014603</v>
       </c>
       <c r="C114">
-        <v>0.7373997761066546</v>
+        <v>0.7432290381133955</v>
       </c>
       <c r="D114">
-        <v>4.209135721102096</v>
+        <v>4.288810422566228</v>
       </c>
       <c r="E114">
-        <v>2.684184448802138E-05</v>
+        <v>1.8872893497E-05</v>
       </c>
     </row>
     <row r="115">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.2825921923585592</v>
+        <v>0.3093300894030289</v>
       </c>
       <c r="C115">
-        <v>0.7375705844415082</v>
+        <v>0.7434011967151858</v>
       </c>
       <c r="D115">
-        <v>0.3831391846687314</v>
+        <v>0.4161011453436501</v>
       </c>
       <c r="E115">
-        <v>0.7016598149055903</v>
+        <v>0.6773834104517267</v>
       </c>
     </row>
     <row r="116">
@@ -2554,16 +2554,16 @@
         </is>
       </c>
       <c r="B116">
-        <v>4.529558366097743</v>
+        <v>4.522546016053618</v>
       </c>
       <c r="C116">
-        <v>0.7375705844415233</v>
+        <v>0.7434011967152011</v>
       </c>
       <c r="D116">
-        <v>6.14118629680365</v>
+        <v>6.083587215136293</v>
       </c>
       <c r="E116">
-        <v>9.965894885626436E-10</v>
+        <v>1.41991147960646E-09</v>
       </c>
     </row>
     <row r="117">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B117">
-        <v>-2.618392125540473</v>
+        <v>-2.580805412562853</v>
       </c>
       <c r="C117">
-        <v>0.7401279791382489</v>
+        <v>0.745978808022</v>
       </c>
       <c r="D117">
-        <v>-3.537755900795884</v>
+        <v>-3.459622960880065</v>
       </c>
       <c r="E117">
-        <v>0.0004133196325001994</v>
+        <v>0.0005529811326498826</v>
       </c>
     </row>
     <row r="118">
@@ -2592,16 +2592,16 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.1137731118102267</v>
+        <v>0.1500838591820562</v>
       </c>
       <c r="C118">
-        <v>0.7375705844414975</v>
+        <v>0.743401196715175</v>
       </c>
       <c r="D118">
-        <v>0.1542538628982579</v>
+        <v>0.2018881054338133</v>
       </c>
       <c r="E118">
-        <v>0.8774261042645213</v>
+        <v>0.8400260088192641</v>
       </c>
     </row>
     <row r="119">
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.546660553968975</v>
+        <v>1.589051166126056</v>
       </c>
       <c r="C119">
-        <v>0.7373997761066019</v>
+        <v>0.7432290381133424</v>
       </c>
       <c r="D119">
-        <v>2.097451889848937</v>
+        <v>2.13803697734927</v>
       </c>
       <c r="E119">
-        <v>0.03608661620835334</v>
+        <v>0.03264214279061955</v>
       </c>
     </row>
     <row r="120">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.7205388381242763</v>
+        <v>-0.6902273631296905</v>
       </c>
       <c r="C120">
-        <v>0.7373997761066361</v>
+        <v>0.7432290381133767</v>
       </c>
       <c r="D120">
-        <v>-0.9771346038760914</v>
+        <v>-0.9286872925226032</v>
       </c>
       <c r="E120">
-        <v>0.3286280339272336</v>
+        <v>0.3531701966337405</v>
       </c>
     </row>
     <row r="121">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="B121">
-        <v>1.620820659868718</v>
+        <v>1.657257972973955</v>
       </c>
       <c r="C121">
-        <v>0.7373997761066089</v>
+        <v>0.7432290381133494</v>
       </c>
       <c r="D121">
-        <v>2.198021632751879</v>
+        <v>2.229807889612096</v>
       </c>
       <c r="E121">
-        <v>0.02806889400427831</v>
+        <v>0.0258776957248848</v>
       </c>
     </row>
     <row r="122">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.4786509851433274</v>
+        <v>-0.4407034693971246</v>
       </c>
       <c r="C122">
-        <v>0.73757058444155</v>
+        <v>0.7434011967152279</v>
       </c>
       <c r="D122">
-        <v>-0.6489561748259484</v>
+        <v>-0.5928205003494814</v>
       </c>
       <c r="E122">
-        <v>0.5164458428142675</v>
+        <v>0.5533724728337813</v>
       </c>
     </row>
     <row r="123">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="B123">
-        <v>1.346451346875818</v>
+        <v>1.390841953887788</v>
       </c>
       <c r="C123">
-        <v>0.7375705844414912</v>
+        <v>0.7434011967151686</v>
       </c>
       <c r="D123">
-        <v>1.825522024980685</v>
+        <v>1.870917023046822</v>
       </c>
       <c r="E123">
-        <v>0.06808061168459643</v>
+        <v>0.06151156796035975</v>
       </c>
     </row>
     <row r="124">
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="B124">
-        <v>4.048565894748949</v>
+        <v>4.043420333615694</v>
       </c>
       <c r="C124">
-        <v>0.7375705844415328</v>
+        <v>0.7434011967152105</v>
       </c>
       <c r="D124">
-        <v>5.489055529260845</v>
+        <v>5.439082357523683</v>
       </c>
       <c r="E124">
-        <v>4.58849367064114E-08</v>
+        <v>6.054613862113221E-08</v>
       </c>
     </row>
     <row r="125">
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.1964683450835211</v>
+        <v>0.2298354045781836</v>
       </c>
       <c r="C125">
-        <v>0.7375705844414923</v>
+        <v>0.7434011967151697</v>
       </c>
       <c r="D125">
-        <v>0.2663722621642945</v>
+        <v>0.3091673857854224</v>
       </c>
       <c r="E125">
-        <v>0.7899816896483718</v>
+        <v>0.7572284061657175</v>
       </c>
     </row>
     <row r="126">
@@ -2744,16 +2744,16 @@
         </is>
       </c>
       <c r="B126">
-        <v>8.756166430374616</v>
+        <v>8.744657909545458</v>
       </c>
       <c r="C126">
-        <v>0.7401279791382137</v>
+        <v>0.7459788080219647</v>
       </c>
       <c r="D126">
-        <v>11.83061129586004</v>
+        <v>11.7223945446021</v>
       </c>
       <c r="E126">
-        <v>3.351625586221884E-31</v>
+        <v>1.107694609284705E-30</v>
       </c>
     </row>
     <row r="127">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="B127">
-        <v>-0.1199390731463374</v>
+        <v>-0.07210907094829269</v>
       </c>
       <c r="C127">
-        <v>0.737570584441498</v>
+        <v>0.7434011967151755</v>
       </c>
       <c r="D127">
-        <v>-0.1626136883389371</v>
+        <v>-0.09699886315345864</v>
       </c>
       <c r="E127">
-        <v>0.8708400569060235</v>
+        <v>0.9227376199189372</v>
       </c>
     </row>
     <row r="128">
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.208426195396152</v>
+        <v>1.253723745766473</v>
       </c>
       <c r="C128">
-        <v>0.7375705844414807</v>
+        <v>0.743401196715158</v>
       </c>
       <c r="D128">
-        <v>1.638387187459791</v>
+        <v>1.686469905222456</v>
       </c>
       <c r="E128">
-        <v>0.1015080164006089</v>
+        <v>0.0918709778817396</v>
       </c>
     </row>
     <row r="129">
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="B129">
-        <v>-3.120009152101895</v>
+        <v>-3.112728522367792</v>
       </c>
       <c r="C129">
-        <v>0.7375705844415268</v>
+        <v>0.7434011967152045</v>
       </c>
       <c r="D129">
-        <v>-4.230116029456762</v>
+        <v>-4.187144890432926</v>
       </c>
       <c r="E129">
-        <v>2.44781670742878E-05</v>
+        <v>2.955177037117135E-05</v>
       </c>
     </row>
     <row r="130">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="B130">
-        <v>-1.843087661864011</v>
+        <v>-1.838283466969223</v>
       </c>
       <c r="C130">
-        <v>0.7375705844414799</v>
+        <v>0.7434011967151573</v>
       </c>
       <c r="D130">
-        <v>-2.498862753941951</v>
+        <v>-2.472801328666117</v>
       </c>
       <c r="E130">
-        <v>0.01254385999210203</v>
+        <v>0.01349358573727454</v>
       </c>
     </row>
     <row r="131">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="B131">
-        <v>-2.754073975075608</v>
+        <v>-2.732750085223806</v>
       </c>
       <c r="C131">
-        <v>0.7373997761066131</v>
+        <v>0.7432290381133537</v>
       </c>
       <c r="D131">
-        <v>-3.734845146843962</v>
+        <v>-3.676861297239869</v>
       </c>
       <c r="E131">
-        <v>0.0001934182368206151</v>
+        <v>0.0002427401101920372</v>
       </c>
     </row>
     <row r="132">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B132">
-        <v>-0.3693702564396894</v>
+        <v>-0.3047686001709704</v>
       </c>
       <c r="C132">
-        <v>0.7375705844415156</v>
+        <v>0.7434011967151931</v>
       </c>
       <c r="D132">
-        <v>-0.5007930959168804</v>
+        <v>-0.4099651729343816</v>
       </c>
       <c r="E132">
-        <v>0.6165752751238729</v>
+        <v>0.6818781310969476</v>
       </c>
     </row>
     <row r="133">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="B133">
-        <v>2.709764381636291</v>
+        <v>2.769277532489008</v>
       </c>
       <c r="C133">
-        <v>0.7373997761065991</v>
+        <v>0.7432290381133396</v>
       </c>
       <c r="D133">
-        <v>3.67475617628146</v>
+        <v>3.726008256510967</v>
       </c>
       <c r="E133">
-        <v>0.0002447357593544955</v>
+        <v>0.0002002711215707271</v>
       </c>
     </row>
     <row r="134">
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="B134">
-        <v>-1.032339041854785</v>
+        <v>-1.023857727291603</v>
       </c>
       <c r="C134">
-        <v>0.7375705844415335</v>
+        <v>0.7434011967152112</v>
       </c>
       <c r="D134">
-        <v>-1.399647794572016</v>
+        <v>-1.377261338582202</v>
       </c>
       <c r="E134">
-        <v>0.1617835338037442</v>
+        <v>0.1685951526316863</v>
       </c>
     </row>
     <row r="135">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B135">
-        <v>4.250845834165171</v>
+        <v>4.264345879923042</v>
       </c>
       <c r="C135">
-        <v>0.7401279791382261</v>
+        <v>0.7459788080219771</v>
       </c>
       <c r="D135">
-        <v>5.743392972543312</v>
+        <v>5.716443730124585</v>
       </c>
       <c r="E135">
-        <v>1.079644496446944E-08</v>
+        <v>1.262097195251857E-08</v>
       </c>
     </row>
     <row r="136">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B136">
-        <v>7.274788947092862</v>
+        <v>7.260333346691263</v>
       </c>
       <c r="C136">
-        <v>0.7375705844415479</v>
+        <v>0.7434011967152258</v>
       </c>
       <c r="D136">
-        <v>9.863176624107066</v>
+        <v>9.766372960887868</v>
       </c>
       <c r="E136">
-        <v>2.077157055552112E-22</v>
+        <v>5.176111284055805E-22</v>
       </c>
     </row>
     <row r="137">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B137">
-        <v>7.659593958390682</v>
+        <v>7.643085634755196</v>
       </c>
       <c r="C137">
-        <v>0.7375705844415485</v>
+        <v>0.7434011967152264</v>
       </c>
       <c r="D137">
-        <v>10.38489619836201</v>
+        <v>10.28123934764531</v>
       </c>
       <c r="E137">
-        <v>1.322022962127055E-24</v>
+        <v>3.676986354791966E-24</v>
       </c>
     </row>
     <row r="138">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B138">
-        <v>7.81257601384304</v>
+        <v>7.804854950965829</v>
       </c>
       <c r="C138">
-        <v>0.7375705844415061</v>
+        <v>0.7434011967151838</v>
       </c>
       <c r="D138">
-        <v>10.59230964282392</v>
+        <v>10.49884636378393</v>
       </c>
       <c r="E138">
-        <v>1.662003066063196E-25</v>
+        <v>4.249913326946902E-25</v>
       </c>
     </row>
     <row r="139">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B139">
-        <v>1.769668174197581</v>
+        <v>1.835515516574772</v>
       </c>
       <c r="C139">
-        <v>0.7375705844415392</v>
+        <v>0.743401196715217</v>
       </c>
       <c r="D139">
-        <v>2.399320433226749</v>
+        <v>2.469077968511697</v>
       </c>
       <c r="E139">
-        <v>0.01652219084251327</v>
+        <v>0.0136343391071374</v>
       </c>
     </row>
     <row r="140">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.410031549485157</v>
+        <v>1.428039764697852</v>
       </c>
       <c r="C140">
-        <v>0.7375705844415202</v>
+        <v>0.7434011967151979</v>
       </c>
       <c r="D140">
-        <v>1.911724218981451</v>
+        <v>1.920954352787978</v>
       </c>
       <c r="E140">
-        <v>0.05606321320759991</v>
+        <v>0.05488829941623027</v>
       </c>
     </row>
     <row r="141">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B141">
-        <v>3.543484506749607</v>
+        <v>3.592867239993262</v>
       </c>
       <c r="C141">
-        <v>0.7375705844414993</v>
+        <v>0.7434011967151767</v>
       </c>
       <c r="D141">
-        <v>4.804264949683144</v>
+        <v>4.83301245124282</v>
       </c>
       <c r="E141">
-        <v>1.676106774825821E-06</v>
+        <v>1.453787636884754E-06</v>
       </c>
     </row>
     <row r="142">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B142">
-        <v>3.663124217690323</v>
+        <v>3.702650265810728</v>
       </c>
       <c r="C142">
-        <v>0.7401279791382374</v>
+        <v>0.7459788080219886</v>
       </c>
       <c r="D142">
-        <v>4.949311904078339</v>
+        <v>4.963479157844372</v>
       </c>
       <c r="E142">
-        <v>8.111151849302631E-07</v>
+        <v>7.548129060893226E-07</v>
       </c>
     </row>
     <row r="143">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B143">
-        <v>6.964775391707956</v>
+        <v>6.980575443677274</v>
       </c>
       <c r="C143">
-        <v>0.7401279791382064</v>
+        <v>0.7459788080219573</v>
       </c>
       <c r="D143">
-        <v>9.410231187067989</v>
+        <v>9.357605562800124</v>
       </c>
       <c r="E143">
-        <v>1.390020682233791E-20</v>
+        <v>2.239668145552375E-20</v>
       </c>
     </row>
     <row r="144">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B144">
-        <v>6.355685070321346</v>
+        <v>6.402960912403083</v>
       </c>
       <c r="C144">
-        <v>0.7401279791382093</v>
+        <v>0.7459788080219601</v>
       </c>
       <c r="D144">
-        <v>8.587278483542512</v>
+        <v>8.583301353266583</v>
       </c>
       <c r="E144">
-        <v>1.834554403752794E-17</v>
+        <v>1.896659635752483E-17</v>
       </c>
     </row>
     <row r="145">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B145">
-        <v>3.375403122784828</v>
+        <v>3.416026650624519</v>
       </c>
       <c r="C145">
-        <v>0.7401279791382397</v>
+        <v>0.7459788080219908</v>
       </c>
       <c r="D145">
-        <v>4.560566845094741</v>
+        <v>4.579254281609321</v>
       </c>
       <c r="E145">
-        <v>5.430112842624967E-06</v>
+        <v>4.971756855582756E-06</v>
       </c>
     </row>
     <row r="146">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B146">
-        <v>-1.059118446805231</v>
+        <v>-1.018879994274402</v>
       </c>
       <c r="C146">
-        <v>0.7375705844415689</v>
+        <v>0.743401196715247</v>
       </c>
       <c r="D146">
-        <v>-1.435955377216017</v>
+        <v>-1.370565448073491</v>
       </c>
       <c r="E146">
-        <v>0.1511811385621897</v>
+        <v>0.170673814367898</v>
       </c>
     </row>
     <row r="147">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B147">
-        <v>-1.071636097606841</v>
+        <v>-1.035746760319166</v>
       </c>
       <c r="C147">
-        <v>0.7401279791382434</v>
+        <v>0.7459788080219946</v>
       </c>
       <c r="D147">
-        <v>-1.447906480788071</v>
+        <v>-1.388439925077104</v>
       </c>
       <c r="E147">
-        <v>0.1478096806632603</v>
+        <v>0.1651673467076052</v>
       </c>
     </row>
     <row r="148">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B148">
-        <v>-0.1843001657428179</v>
+        <v>-0.146588141988205</v>
       </c>
       <c r="C148">
-        <v>0.7375705844415125</v>
+        <v>0.74340119671519</v>
       </c>
       <c r="D148">
-        <v>-0.2498746148917662</v>
+        <v>-0.1971857761810484</v>
       </c>
       <c r="E148">
-        <v>0.8027115713006807</v>
+        <v>0.8437034423916918</v>
       </c>
     </row>
     <row r="149">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B149">
-        <v>-2.52763483566286</v>
+        <v>-2.507773624462408</v>
       </c>
       <c r="C149">
-        <v>0.7375705844415349</v>
+        <v>0.7434011967152128</v>
       </c>
       <c r="D149">
-        <v>-3.426973484275684</v>
+        <v>-3.373378514244043</v>
       </c>
       <c r="E149">
-        <v>0.0006234684299254802</v>
+        <v>0.000757563790885116</v>
       </c>
     </row>
     <row r="150">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.09534891498959548</v>
+        <v>0.1489847063921493</v>
       </c>
       <c r="C150">
-        <v>0.7375705844415368</v>
+        <v>0.7434011967152145</v>
       </c>
       <c r="D150">
-        <v>0.1292742918452889</v>
+        <v>0.2004095595358895</v>
       </c>
       <c r="E150">
-        <v>0.8971544192957943</v>
+        <v>0.8411819257908676</v>
       </c>
     </row>
     <row r="151">
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="B151">
-        <v>-1.181551820026384</v>
+        <v>-1.141087448855888</v>
       </c>
       <c r="C151">
-        <v>0.7373997761065869</v>
+        <v>0.7432290381133272</v>
       </c>
       <c r="D151">
-        <v>-1.602321913175626</v>
+        <v>-1.535310638228717</v>
       </c>
       <c r="E151">
-        <v>0.1092521658774115</v>
+        <v>0.1248755403561703</v>
       </c>
     </row>
     <row r="152">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B152">
-        <v>1.718675269627903</v>
+        <v>1.759983466729502</v>
       </c>
       <c r="C152">
-        <v>0.7373997761066376</v>
+        <v>0.7432290381133784</v>
       </c>
       <c r="D152">
-        <v>2.330723883186208</v>
+        <v>2.368023013736204</v>
       </c>
       <c r="E152">
-        <v>0.0198730344682956</v>
+        <v>0.01798393085909786</v>
       </c>
     </row>
     <row r="153">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.02115448928822474</v>
+        <v>0.06576148595063862</v>
       </c>
       <c r="C153">
-        <v>0.7375705844415497</v>
+        <v>0.7434011967152275</v>
       </c>
       <c r="D153">
-        <v>0.0286813082496258</v>
+        <v>0.08846029067643493</v>
       </c>
       <c r="E153">
-        <v>0.9771218034242254</v>
+        <v>0.9295202506707908</v>
       </c>
     </row>
     <row r="154">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B154">
-        <v>-0.6760072891860968</v>
+        <v>-0.6319321672556719</v>
       </c>
       <c r="C154">
-        <v>0.7375705844415231</v>
+        <v>0.7434011967152008</v>
       </c>
       <c r="D154">
-        <v>-0.9165323339161618</v>
+        <v>-0.8500553537550559</v>
       </c>
       <c r="E154">
-        <v>0.3595051213728331</v>
+        <v>0.3954023805777801</v>
       </c>
     </row>
     <row r="155">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B155">
-        <v>-1.464766727049337</v>
+        <v>-1.406475973840655</v>
       </c>
       <c r="C155">
-        <v>0.7401279791382445</v>
+        <v>0.7459788080219956</v>
       </c>
       <c r="D155">
-        <v>-1.97907222579913</v>
+        <v>-1.885410093042729</v>
       </c>
       <c r="E155">
-        <v>0.04795334022519448</v>
+        <v>0.05952832455543332</v>
       </c>
     </row>
     <row r="156">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B156">
-        <v>-1.521785070261928</v>
+        <v>-1.510867862815711</v>
       </c>
       <c r="C156">
-        <v>0.7375705844415026</v>
+        <v>0.7434011967151801</v>
       </c>
       <c r="D156">
-        <v>-2.063239915423474</v>
+        <v>-2.032372115476391</v>
       </c>
       <c r="E156">
-        <v>0.03922663560448575</v>
+        <v>0.0422560829201746</v>
       </c>
     </row>
     <row r="157">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B157">
-        <v>-0.9280654015689572</v>
+        <v>-0.9011016494490575</v>
       </c>
       <c r="C157">
-        <v>0.7375705844415128</v>
+        <v>0.7434011967151903</v>
       </c>
       <c r="D157">
-        <v>-1.258273338370302</v>
+        <v>-1.212133708461442</v>
       </c>
       <c r="E157">
-        <v>0.2084489150841515</v>
+        <v>0.2256132706368289</v>
       </c>
     </row>
     <row r="158">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B158">
-        <v>0.414367930401648</v>
+        <v>0.4835664196837061</v>
       </c>
       <c r="C158">
-        <v>0.7375705844415521</v>
+        <v>0.74340119671523</v>
       </c>
       <c r="D158">
-        <v>0.5618010521872759</v>
+        <v>0.6504783982328494</v>
       </c>
       <c r="E158">
-        <v>0.5743184355386427</v>
+        <v>0.5154626075362898</v>
       </c>
     </row>
     <row r="159">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B159">
-        <v>3.78268768221788</v>
+        <v>3.780824408885576</v>
       </c>
       <c r="C159">
-        <v>0.7401279791382588</v>
+        <v>0.74597880802201</v>
       </c>
       <c r="D159">
-        <v>5.110856215194182</v>
+        <v>5.068273211286751</v>
       </c>
       <c r="E159">
-        <v>3.532079296044503E-07</v>
+        <v>4.407821496967976E-07</v>
       </c>
     </row>
     <row r="160">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B160">
-        <v>3.064583583749803</v>
+        <v>3.102417652932195</v>
       </c>
       <c r="C160">
-        <v>0.7373997761066404</v>
+        <v>0.7432290381133811</v>
       </c>
       <c r="D160">
-        <v>4.155932349112367</v>
+        <v>4.174241712631948</v>
       </c>
       <c r="E160">
-        <v>3.384825652855146E-05</v>
+        <v>3.126094170162709E-05</v>
       </c>
     </row>
     <row r="161">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B161">
-        <v>0.1162830072447792</v>
+        <v>0.1728751376535292</v>
       </c>
       <c r="C161">
-        <v>0.7375705844415332</v>
+        <v>0.7434011967152111</v>
       </c>
       <c r="D161">
-        <v>0.1576567852591699</v>
+        <v>0.2325462192116375</v>
       </c>
       <c r="E161">
-        <v>0.8747441584572228</v>
+        <v>0.8161390651495442</v>
       </c>
     </row>
     <row r="162">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B162">
-        <v>-2.592652708243988</v>
+        <v>-2.573109350769289</v>
       </c>
       <c r="C162">
-        <v>0.7373997761066321</v>
+        <v>0.7432290381133728</v>
       </c>
       <c r="D162">
-        <v>-3.515939104203194</v>
+        <v>-3.462067840219107</v>
       </c>
       <c r="E162">
-        <v>0.0004485732651496966</v>
+        <v>0.0005480137150513576</v>
       </c>
     </row>
     <row r="163">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.5041522149974493</v>
+        <v>-0.4531600533964429</v>
       </c>
       <c r="C163">
-        <v>0.7373997761066037</v>
+        <v>0.7432290381133442</v>
       </c>
       <c r="D163">
-        <v>-0.6836891348941304</v>
+        <v>-0.6097179068067238</v>
       </c>
       <c r="E163">
-        <v>0.4942556062906404</v>
+        <v>0.5421222552491838</v>
       </c>
     </row>
     <row r="164">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B164">
-        <v>1.133906328506992</v>
+        <v>1.191815587805446</v>
       </c>
       <c r="C164">
-        <v>0.7373997761066052</v>
+        <v>0.7432290381133456</v>
       </c>
       <c r="D164">
-        <v>1.537709076200023</v>
+        <v>1.603564347850049</v>
       </c>
       <c r="E164">
-        <v>0.1242877732566648</v>
+        <v>0.1089778213428308</v>
       </c>
     </row>
     <row r="165">
@@ -3485,16 +3485,16 @@
         </is>
       </c>
       <c r="B165">
-        <v>3.347309683463713</v>
+        <v>3.354835916237518</v>
       </c>
       <c r="C165">
-        <v>0.7373997761066218</v>
+        <v>0.7432290381133624</v>
       </c>
       <c r="D165">
-        <v>4.539341876582996</v>
+        <v>4.513865503362929</v>
       </c>
       <c r="E165">
-        <v>5.999809885338429E-06</v>
+        <v>6.759349969487861E-06</v>
       </c>
     </row>
     <row r="166">
@@ -3504,16 +3504,16 @@
         </is>
       </c>
       <c r="B166">
-        <v>1.993349050972492</v>
+        <v>2.000525076759492</v>
       </c>
       <c r="C166">
-        <v>0.7375705844415614</v>
+        <v>0.7434011967152394</v>
       </c>
       <c r="D166">
-        <v>2.702587512328357</v>
+        <v>2.691043659330825</v>
       </c>
       <c r="E166">
-        <v>0.006941998709981233</v>
+        <v>0.00718588175274714</v>
       </c>
     </row>
     <row r="167">
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B167">
-        <v>3.695239896819154</v>
+        <v>3.753169781224609</v>
       </c>
       <c r="C167">
-        <v>0.7375705844415184</v>
+        <v>0.743401196715196</v>
       </c>
       <c r="D167">
-        <v>5.010015278222024</v>
+        <v>5.048646407630796</v>
       </c>
       <c r="E167">
-        <v>5.95173300239154E-07</v>
+        <v>4.878815304002897E-07</v>
       </c>
     </row>
     <row r="168">
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="B168">
-        <v>4.139808387420829</v>
+        <v>4.16001799951683</v>
       </c>
       <c r="C168">
-        <v>0.7375705844414964</v>
+        <v>0.7434011967151738</v>
       </c>
       <c r="D168">
-        <v>5.612762323697572</v>
+        <v>5.595925884836443</v>
       </c>
       <c r="E168">
-        <v>2.287021444256147E-08</v>
+        <v>2.516447119901765E-08</v>
       </c>
     </row>
     <row r="169">
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="B169">
-        <v>3.985060347725975</v>
+        <v>4.02467347970599</v>
       </c>
       <c r="C169">
-        <v>0.7375705844415237</v>
+        <v>0.7434011967152013</v>
       </c>
       <c r="D169">
-        <v>5.402954553486426</v>
+        <v>5.413864676959689</v>
       </c>
       <c r="E169">
-        <v>7.387811456875733E-08</v>
+        <v>6.95777776778649E-08</v>
       </c>
     </row>
     <row r="170">
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.770346727563906</v>
+        <v>1.836985288917947</v>
       </c>
       <c r="C170">
-        <v>0.7375705844415417</v>
+        <v>0.7434011967152194</v>
       </c>
       <c r="D170">
-        <v>2.400240417538262</v>
+        <v>2.471055060221615</v>
       </c>
       <c r="E170">
-        <v>0.01648085098631662</v>
+        <v>0.01355943874259473</v>
       </c>
     </row>
     <row r="171">
@@ -3599,16 +3599,16 @@
         </is>
       </c>
       <c r="B171">
-        <v>1.619106621504042</v>
+        <v>1.624704163802667</v>
       </c>
       <c r="C171">
-        <v>0.7373997761066319</v>
+        <v>0.7432290381133725</v>
       </c>
       <c r="D171">
-        <v>2.195697197051916</v>
+        <v>2.186007381959737</v>
       </c>
       <c r="E171">
-        <v>0.02823523185154631</v>
+        <v>0.02893782999395854</v>
       </c>
     </row>
     <row r="172">
@@ -3618,16 +3618,16 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.901991358250047</v>
+        <v>1.989925069934134</v>
       </c>
       <c r="C172">
-        <v>0.7375705844415023</v>
+        <v>0.7434011967151797</v>
       </c>
       <c r="D172">
-        <v>2.578724529382173</v>
+        <v>2.676784862234406</v>
       </c>
       <c r="E172">
-        <v>0.009991878501666994</v>
+        <v>0.00749773168697001</v>
       </c>
     </row>
     <row r="173">
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="B173">
-        <v>1.184859038093933</v>
+        <v>1.271062257213694</v>
       </c>
       <c r="C173">
-        <v>0.737570584441519</v>
+        <v>0.7434011967151966</v>
       </c>
       <c r="D173">
-        <v>1.606434778023444</v>
+        <v>1.709793127627488</v>
       </c>
       <c r="E173">
-        <v>0.1083460809888439</v>
+        <v>0.0874688831069524</v>
       </c>
     </row>
     <row r="174">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.2672964104311918</v>
+        <v>0.3515449038182363</v>
       </c>
       <c r="C174">
-        <v>0.7401279791382337</v>
+        <v>0.7459788080219848</v>
       </c>
       <c r="D174">
-        <v>0.3611489066288479</v>
+        <v>0.4712532045653982</v>
       </c>
       <c r="E174">
-        <v>0.7180286486463279</v>
+        <v>0.6375145200850092</v>
       </c>
     </row>
     <row r="175">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B175">
-        <v>1.96472035745452</v>
+        <v>1.97315921346731</v>
       </c>
       <c r="C175">
-        <v>0.7375705844415421</v>
+        <v>0.7434011967152199</v>
       </c>
       <c r="D175">
-        <v>2.663772659727373</v>
+        <v>2.654231957368213</v>
       </c>
       <c r="E175">
-        <v>0.00779286017531098</v>
+        <v>0.008015826545571017</v>
       </c>
     </row>
     <row r="176">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="B176">
-        <v>3.615624064637277</v>
+        <v>3.629500697759295</v>
       </c>
       <c r="C176">
-        <v>0.7375705844415337</v>
+        <v>0.7434011967152114</v>
       </c>
       <c r="D176">
-        <v>4.90207193847748</v>
+        <v>4.882290630949462</v>
       </c>
       <c r="E176">
-        <v>1.029619551906752E-06</v>
+        <v>1.137073981621692E-06</v>
       </c>
     </row>
     <row r="177">
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.8553500103135262</v>
+        <v>-0.8462951042642126</v>
       </c>
       <c r="C177">
-        <v>0.7375705844415082</v>
+        <v>0.7434011967151858</v>
       </c>
       <c r="D177">
-        <v>-1.159685633289187</v>
+        <v>-1.138409660898687</v>
       </c>
       <c r="E177">
-        <v>0.2463238468919698</v>
+        <v>0.2550942778382219</v>
       </c>
     </row>
     <row r="178">
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="B178">
-        <v>1.192764237199183</v>
+        <v>1.251167007967816</v>
       </c>
       <c r="C178">
-        <v>0.7375705844415303</v>
+        <v>0.743401196715208</v>
       </c>
       <c r="D178">
-        <v>1.617152666279816</v>
+        <v>1.683030661634958</v>
       </c>
       <c r="E178">
-        <v>0.1060128265767857</v>
+        <v>0.09253492818278389</v>
       </c>
     </row>
     <row r="179">
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="B179">
-        <v>1.302092902961893</v>
+        <v>1.324015254054118</v>
       </c>
       <c r="C179">
-        <v>0.7373997761066036</v>
+        <v>0.743229038113344</v>
       </c>
       <c r="D179">
-        <v>1.765789664104337</v>
+        <v>1.781436389265785</v>
       </c>
       <c r="E179">
-        <v>0.07759317431080061</v>
+        <v>0.07500232554817288</v>
       </c>
     </row>
     <row r="180">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B180">
-        <v>0.8942167875542083</v>
+        <v>0.9264064278842635</v>
       </c>
       <c r="C180">
-        <v>0.7375705844415112</v>
+        <v>0.7434011967151888</v>
       </c>
       <c r="D180">
-        <v>1.212381304809369</v>
+        <v>1.246172903645711</v>
       </c>
       <c r="E180">
-        <v>0.2255185446805759</v>
+        <v>0.2128559381866985</v>
       </c>
     </row>
     <row r="181">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="B181">
-        <v>-1.456783777350581</v>
+        <v>-1.426340574277833</v>
       </c>
       <c r="C181">
-        <v>0.7375705844415313</v>
+        <v>0.7434011967152091</v>
       </c>
       <c r="D181">
-        <v>-1.975111003719892</v>
+        <v>-1.918668655068432</v>
       </c>
       <c r="E181">
-        <v>0.04840140102923472</v>
+        <v>0.05517731726053429</v>
       </c>
     </row>
     <row r="182">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B182">
-        <v>2.011129028840761</v>
+        <v>2.00936256162926</v>
       </c>
       <c r="C182">
-        <v>0.7375705844415008</v>
+        <v>0.7434011967151783</v>
       </c>
       <c r="D182">
-        <v>2.726693649752339</v>
+        <v>2.70293156711061</v>
       </c>
       <c r="E182">
-        <v>0.006456560260308274</v>
+        <v>0.00693484556090145</v>
       </c>
     </row>
     <row r="183">
@@ -3827,16 +3827,16 @@
         </is>
       </c>
       <c r="B183">
-        <v>0.9344789033913237</v>
+        <v>0.9567825511710498</v>
       </c>
       <c r="C183">
-        <v>0.737570584441502</v>
+        <v>0.7434011967151796</v>
       </c>
       <c r="D183">
-        <v>1.266968779806916</v>
+        <v>1.287033913045506</v>
       </c>
       <c r="E183">
-        <v>0.2053231321146422</v>
+        <v>0.1982406534773203</v>
       </c>
     </row>
     <row r="184">
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="B184">
-        <v>1.495421038490256</v>
+        <v>1.551761508871494</v>
       </c>
       <c r="C184">
-        <v>0.7375705844415179</v>
+        <v>0.7434011967151956</v>
       </c>
       <c r="D184">
-        <v>2.027495496749746</v>
+        <v>2.087380967004267</v>
       </c>
       <c r="E184">
-        <v>0.04275235721384799</v>
+        <v>0.03698785865187346</v>
       </c>
     </row>
     <row r="185">
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B185">
-        <v>4.075285987751132</v>
+        <v>4.11856063829387</v>
       </c>
       <c r="C185">
-        <v>0.737399776106622</v>
+        <v>0.7432290381133626</v>
       </c>
       <c r="D185">
-        <v>5.52656255100609</v>
+        <v>5.541442041538852</v>
       </c>
       <c r="E185">
-        <v>3.720776461901329E-08</v>
+        <v>3.422644411743376E-08</v>
       </c>
     </row>
     <row r="186">
@@ -3884,16 +3884,16 @@
         </is>
       </c>
       <c r="B186">
-        <v>3.643123216630718</v>
+        <v>3.69090150830338</v>
       </c>
       <c r="C186">
-        <v>0.7373997761066295</v>
+        <v>0.7432290381133702</v>
       </c>
       <c r="D186">
-        <v>4.940499488440196</v>
+        <v>4.96603512380578</v>
       </c>
       <c r="E186">
-        <v>8.481562151907219E-07</v>
+        <v>7.450647236815262E-07</v>
       </c>
     </row>
     <row r="187">
@@ -3903,16 +3903,16 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.6646326334083278</v>
+        <v>0.7235583064404882</v>
       </c>
       <c r="C187">
-        <v>0.7373997761066209</v>
+        <v>0.7432290381133615</v>
       </c>
       <c r="D187">
-        <v>0.9013192774718558</v>
+        <v>0.9735334188195793</v>
       </c>
       <c r="E187">
-        <v>0.3675338521574032</v>
+        <v>0.3304133012830811</v>
       </c>
     </row>
     <row r="188">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="B188">
-        <v>1.411562280383374</v>
+        <v>1.415862585396024</v>
       </c>
       <c r="C188">
-        <v>0.7373997761066182</v>
+        <v>0.7432290381133587</v>
       </c>
       <c r="D188">
-        <v>1.914242892554501</v>
+        <v>1.905015160589129</v>
       </c>
       <c r="E188">
-        <v>0.05574054771689613</v>
+        <v>0.05693030932026578</v>
       </c>
     </row>
     <row r="189">
@@ -3941,16 +3941,16 @@
         </is>
       </c>
       <c r="B189">
-        <v>2.112133195763815</v>
+        <v>2.147392900637523</v>
       </c>
       <c r="C189">
-        <v>0.7375705844415055</v>
+        <v>0.743401196715183</v>
       </c>
       <c r="D189">
-        <v>2.863635345982703</v>
+        <v>2.888605654828192</v>
       </c>
       <c r="E189">
-        <v>0.004234469500759432</v>
+        <v>0.003913759179510089</v>
       </c>
     </row>
     <row r="190">
@@ -3960,16 +3960,16 @@
         </is>
       </c>
       <c r="B190">
-        <v>0.929723066273226</v>
+        <v>1.000039822355355</v>
       </c>
       <c r="C190">
-        <v>0.7373997761066097</v>
+        <v>0.7432290381133501</v>
       </c>
       <c r="D190">
-        <v>1.260812786223048</v>
+        <v>1.345533840946132</v>
       </c>
       <c r="E190">
-        <v>0.2075325026532457</v>
+        <v>0.1786148972906745</v>
       </c>
     </row>
     <row r="191">
@@ -3979,16 +3979,16 @@
         </is>
       </c>
       <c r="B191">
-        <v>2.234364930340422</v>
+        <v>2.276609745938085</v>
       </c>
       <c r="C191">
-        <v>0.7373997761066167</v>
+        <v>0.7432290381133572</v>
       </c>
       <c r="D191">
-        <v>3.030059138528091</v>
+        <v>3.063133474597714</v>
       </c>
       <c r="E191">
-        <v>0.00247833852842764</v>
+        <v>0.00222135021363059</v>
       </c>
     </row>
     <row r="192">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="B192">
-        <v>0.1718204039964449</v>
+        <v>0.2164771443022301</v>
       </c>
       <c r="C192">
-        <v>0.737570584441512</v>
+        <v>0.7434011967151896</v>
       </c>
       <c r="D192">
-        <v>0.2329545234325568</v>
+        <v>0.2911982725596369</v>
       </c>
       <c r="E192">
-        <v>0.8158220377996406</v>
+        <v>0.7709317554074209</v>
       </c>
     </row>
     <row r="193">
@@ -4017,16 +4017,16 @@
         </is>
       </c>
       <c r="B193">
-        <v>4.000492131016323</v>
+        <v>4.013366396044203</v>
       </c>
       <c r="C193">
-        <v>0.7373997761066043</v>
+        <v>0.7432290381133447</v>
       </c>
       <c r="D193">
-        <v>5.425133368141924</v>
+        <v>5.399905265047183</v>
       </c>
       <c r="E193">
-        <v>6.539116736320961E-08</v>
+        <v>7.512537961556573E-08</v>
       </c>
     </row>
     <row r="194">
@@ -4036,16 +4036,16 @@
         </is>
       </c>
       <c r="B194">
-        <v>0.5150335064439845</v>
+        <v>0.5922991888103916</v>
       </c>
       <c r="C194">
-        <v>0.737399776106611</v>
+        <v>0.7432290381133515</v>
       </c>
       <c r="D194">
-        <v>0.6984454337148084</v>
+        <v>0.796926867004433</v>
       </c>
       <c r="E194">
-        <v>0.4849849176881968</v>
+        <v>0.4255939755493703</v>
       </c>
     </row>
     <row r="195">
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.6774915998652444</v>
+        <v>0.7508750366045814</v>
       </c>
       <c r="C195">
-        <v>0.7375705844415118</v>
+        <v>0.7434011967151892</v>
       </c>
       <c r="D195">
-        <v>0.9185447659605905</v>
+        <v>1.010053575273239</v>
       </c>
       <c r="E195">
-        <v>0.3584513748860897</v>
+        <v>0.3125993934649805</v>
       </c>
     </row>
     <row r="196">
@@ -4074,16 +4074,16 @@
         </is>
       </c>
       <c r="B196">
-        <v>2.78600320555166</v>
+        <v>2.806388641889916</v>
       </c>
       <c r="C196">
-        <v>0.7373997761065979</v>
+        <v>0.7432290381133383</v>
       </c>
       <c r="D196">
-        <v>3.778144902974472</v>
+        <v>3.775940521664544</v>
       </c>
       <c r="E196">
-        <v>0.0001629119030372386</v>
+        <v>0.0001643486278171331</v>
       </c>
     </row>
     <row r="197">
@@ -4093,16 +4093,16 @@
         </is>
       </c>
       <c r="B197">
-        <v>0.7504363513895042</v>
+        <v>0.8108199714041496</v>
       </c>
       <c r="C197">
-        <v>0.7373997761066038</v>
+        <v>0.7432290381133443</v>
       </c>
       <c r="D197">
-        <v>1.017679114783208</v>
+        <v>1.090942266548657</v>
       </c>
       <c r="E197">
-        <v>0.308961212203002</v>
+        <v>0.2754378621083701</v>
       </c>
     </row>
     <row r="198">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.198925793086062</v>
+        <v>0.2266886774069165</v>
       </c>
       <c r="C198">
-        <v>0.7373997761066197</v>
+        <v>0.7432290381133603</v>
       </c>
       <c r="D198">
-        <v>0.2697665493422927</v>
+        <v>0.3050051407872212</v>
       </c>
       <c r="E198">
-        <v>0.7873694179829278</v>
+        <v>0.7603959452510146</v>
       </c>
     </row>
     <row r="199">
@@ -4131,16 +4131,16 @@
         </is>
       </c>
       <c r="B199">
-        <v>0.7576600180337918</v>
+        <v>0.8214623589824458</v>
       </c>
       <c r="C199">
-        <v>0.7373997761066118</v>
+        <v>0.7432290381133523</v>
       </c>
       <c r="D199">
-        <v>1.027475248275978</v>
+        <v>1.105261388962526</v>
       </c>
       <c r="E199">
-        <v>0.3043286999651186</v>
+        <v>0.2691875425608735</v>
       </c>
     </row>
     <row r="200">
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="B200">
-        <v>4.990079117418927</v>
+        <v>5.025956893884609</v>
       </c>
       <c r="C200">
-        <v>0.737399776106603</v>
+        <v>0.7432290381133434</v>
       </c>
       <c r="D200">
-        <v>6.767128603925058</v>
+        <v>6.762325792117589</v>
       </c>
       <c r="E200">
-        <v>1.748379111218791E-11</v>
+        <v>1.805925249635485E-11</v>
       </c>
     </row>
     <row r="201">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="B201">
-        <v>0.4381261791683101</v>
+        <v>0.4668480444647434</v>
       </c>
       <c r="C201">
-        <v>0.7373997761066226</v>
+        <v>0.743229038113363</v>
       </c>
       <c r="D201">
-        <v>0.5941501385877289</v>
+        <v>0.6281348285984705</v>
       </c>
       <c r="E201">
-        <v>0.5524830715211129</v>
+        <v>0.5299917919237511</v>
       </c>
     </row>
     <row r="202">
@@ -4188,16 +4188,16 @@
         </is>
       </c>
       <c r="B202">
-        <v>-0.4690815038673417</v>
+        <v>-0.4379002301772306</v>
       </c>
       <c r="C202">
-        <v>0.7373997761066183</v>
+        <v>0.7432290381133588</v>
       </c>
       <c r="D202">
-        <v>-0.6361291650290909</v>
+        <v>-0.5891861158826804</v>
       </c>
       <c r="E202">
-        <v>0.5247695473763143</v>
+        <v>0.5558071064659755</v>
       </c>
     </row>
     <row r="203">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B203">
-        <v>5.324837609639526</v>
+        <v>5.441533044339697</v>
       </c>
       <c r="C203">
-        <v>0.7373997761066305</v>
+        <v>0.7432290381133713</v>
       </c>
       <c r="D203">
-        <v>7.221100117162954</v>
+        <v>7.321475299394387</v>
       </c>
       <c r="E203">
-        <v>7.450934731018318E-13</v>
+        <v>3.61635944391562E-13</v>
       </c>
     </row>
     <row r="204">
@@ -4226,16 +4226,16 @@
         </is>
       </c>
       <c r="B204">
-        <v>-1.548434087524109</v>
+        <v>-1.49360578762753</v>
       </c>
       <c r="C204">
-        <v>0.7373997761066274</v>
+        <v>0.743229038113368</v>
       </c>
       <c r="D204">
-        <v>-2.099857007957928</v>
+        <v>-2.009617104599328</v>
       </c>
       <c r="E204">
-        <v>0.03587417632492713</v>
+        <v>0.04461415965142545</v>
       </c>
     </row>
     <row r="205">
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="B205">
-        <v>-0.3460855897983235</v>
+        <v>-0.3165582321060803</v>
       </c>
       <c r="C205">
-        <v>0.7373997761066063</v>
+        <v>0.7432290381133468</v>
       </c>
       <c r="D205">
-        <v>-0.4693323771070548</v>
+        <v>-0.42592285267762</v>
       </c>
       <c r="E205">
-        <v>0.6388864136304351</v>
+        <v>0.6702127404258866</v>
       </c>
     </row>
     <row r="206">
@@ -4264,16 +4264,16 @@
         </is>
       </c>
       <c r="B206">
-        <v>0.3621913755954311</v>
+        <v>0.4362190888401219</v>
       </c>
       <c r="C206">
-        <v>0.7373997761066142</v>
+        <v>0.7432290381133547</v>
       </c>
       <c r="D206">
-        <v>0.4911736988960857</v>
+        <v>0.586924173398068</v>
       </c>
       <c r="E206">
-        <v>0.6233608397608752</v>
+        <v>0.5573249935999985</v>
       </c>
     </row>
     <row r="207">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="B207">
-        <v>-2.20577885047653</v>
+        <v>-2.174738092801115</v>
       </c>
       <c r="C207">
-        <v>0.7373997761066262</v>
+        <v>0.7432290381133669</v>
       </c>
       <c r="D207">
-        <v>-2.991293084089002</v>
+        <v>-2.926067176171602</v>
       </c>
       <c r="E207">
-        <v>0.00281405393084293</v>
+        <v>0.003473882885583735</v>
       </c>
     </row>
     <row r="208">
@@ -4302,16 +4302,16 @@
         </is>
       </c>
       <c r="B208">
-        <v>5.483910244840183</v>
+        <v>5.554534925245147</v>
       </c>
       <c r="C208">
-        <v>0.7373997761066168</v>
+        <v>0.7432290381133573</v>
       </c>
       <c r="D208">
-        <v>7.43682114170766</v>
+        <v>7.473517099580776</v>
       </c>
       <c r="E208">
-        <v>1.558262653091934E-13</v>
+        <v>1.189130297350801E-13</v>
       </c>
     </row>
     <row r="209">
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="B209">
-        <v>0.2001692384158138</v>
+        <v>0.2766774236919328</v>
       </c>
       <c r="C209">
-        <v>0.7373997761066297</v>
+        <v>0.7432290381133704</v>
       </c>
       <c r="D209">
-        <v>0.2714528060649545</v>
+        <v>0.3722640121734979</v>
       </c>
       <c r="E209">
-        <v>0.7860725483907861</v>
+        <v>0.7097381812514649</v>
       </c>
     </row>
     <row r="210">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="B210">
-        <v>-0.09009345268486188</v>
+        <v>-0.03426121452963419</v>
       </c>
       <c r="C210">
-        <v>0.7373997761066192</v>
+        <v>0.7432290381133598</v>
       </c>
       <c r="D210">
-        <v>-0.1221772173034067</v>
+        <v>-0.04609778785904831</v>
       </c>
       <c r="E210">
-        <v>0.9027717064240706</v>
+        <v>0.9632371972834661</v>
       </c>
     </row>
     <row r="211">
@@ -4359,16 +4359,16 @@
         </is>
       </c>
       <c r="B211">
-        <v>3.386067900581153</v>
+        <v>3.369900064954695</v>
       </c>
       <c r="C211">
-        <v>0.7373997761066081</v>
+        <v>0.7432290381133486</v>
       </c>
       <c r="D211">
-        <v>4.591902534144002</v>
+        <v>4.534134018107022</v>
       </c>
       <c r="E211">
-        <v>4.682825414030555E-06</v>
+        <v>6.148101643281601E-06</v>
       </c>
     </row>
     <row r="212">
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="B212">
-        <v>10.98787563641042</v>
+        <v>10.97882066960614</v>
       </c>
       <c r="C212">
-        <v>0.7373997761066188</v>
+        <v>0.7432290381133594</v>
       </c>
       <c r="D212">
-        <v>14.90083939871133</v>
+        <v>14.77178649730263</v>
       </c>
       <c r="E212">
-        <v>1.49233491878798E-47</v>
+        <v>8.350539846608979E-47</v>
       </c>
     </row>
     <row r="213">
@@ -4397,16 +4397,16 @@
         </is>
       </c>
       <c r="B213">
-        <v>0.05950324901970545</v>
+        <v>0.06872263115154197</v>
       </c>
       <c r="C213">
-        <v>0.7375705844415198</v>
+        <v>0.7434011967151974</v>
       </c>
       <c r="D213">
-        <v>0.08067465036551132</v>
+        <v>0.09244353043175167</v>
       </c>
       <c r="E213">
-        <v>0.9357092703475856</v>
+        <v>0.9263554888968113</v>
       </c>
     </row>
     <row r="214">
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="B214">
-        <v>2.818072703346258</v>
+        <v>2.821351892940839</v>
       </c>
       <c r="C214">
-        <v>0.7373997761066143</v>
+        <v>0.7432290381133548</v>
       </c>
       <c r="D214">
-        <v>3.82163487792925</v>
+        <v>3.79607328059017</v>
       </c>
       <c r="E214">
-        <v>0.000136874220270152</v>
+        <v>0.0001516584753519501</v>
       </c>
     </row>
     <row r="215">
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="B215">
-        <v>3.462684724256626</v>
+        <v>3.475840303572692</v>
       </c>
       <c r="C215">
-        <v>0.7373997761066196</v>
+        <v>0.7432290381133602</v>
       </c>
       <c r="D215">
-        <v>4.695803872546825</v>
+        <v>4.676674517986935</v>
       </c>
       <c r="E215">
-        <v>2.847527809811014E-06</v>
+        <v>3.122988187000535E-06</v>
       </c>
     </row>
     <row r="216">
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="B216">
-        <v>1.489242268113679</v>
+        <v>1.502461591144782</v>
       </c>
       <c r="C216">
-        <v>0.73739977610662</v>
+        <v>0.7432290381133606</v>
       </c>
       <c r="D216">
-        <v>2.019586005269347</v>
+        <v>2.021532413424917</v>
       </c>
       <c r="E216">
-        <v>0.04356775889271335</v>
+        <v>0.04336589080419388</v>
       </c>
     </row>
     <row r="217">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="B217">
-        <v>3.116364737262363</v>
+        <v>3.140872616359107</v>
       </c>
       <c r="C217">
-        <v>0.7373997761066118</v>
+        <v>0.7432290381133523</v>
       </c>
       <c r="D217">
-        <v>4.22615362553596</v>
+        <v>4.225982106851</v>
       </c>
       <c r="E217">
-        <v>2.490883014365846E-05</v>
+        <v>2.492763398115585E-05</v>
       </c>
     </row>
     <row r="218">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="B218">
-        <v>1.619557188166601</v>
+        <v>1.625023839606841</v>
       </c>
       <c r="C218">
-        <v>0.7373997761066114</v>
+        <v>0.7432290381133519</v>
       </c>
       <c r="D218">
-        <v>2.196308217935301</v>
+        <v>2.186437499444154</v>
       </c>
       <c r="E218">
-        <v>0.02819142472148607</v>
+        <v>0.02890632612595913</v>
       </c>
     </row>
     <row r="219">
@@ -4511,16 +4511,16 @@
         </is>
       </c>
       <c r="B219">
-        <v>2.608386237543942</v>
+        <v>2.629354500934165</v>
       </c>
       <c r="C219">
-        <v>0.7373997761066079</v>
+        <v>0.7432290381133484</v>
       </c>
       <c r="D219">
-        <v>3.537275602816077</v>
+        <v>3.537744579529153</v>
       </c>
       <c r="E219">
-        <v>0.0004140670447739589</v>
+        <v>0.000413337235487154</v>
       </c>
     </row>
     <row r="220">
@@ -4530,16 +4530,16 @@
         </is>
       </c>
       <c r="B220">
-        <v>-3.130027440199083</v>
+        <v>-3.093318643995782</v>
       </c>
       <c r="C220">
-        <v>0.7401279791382351</v>
+        <v>0.7459788080219862</v>
       </c>
       <c r="D220">
-        <v>-4.229035421473347</v>
+        <v>-4.146657533339221</v>
       </c>
       <c r="E220">
-        <v>2.459490712891046E-05</v>
+        <v>3.523533804196076E-05</v>
       </c>
     </row>
     <row r="221">
@@ -4549,16 +4549,16 @@
         </is>
       </c>
       <c r="B221">
-        <v>3.67553390638219</v>
+        <v>3.674999780462023</v>
       </c>
       <c r="C221">
-        <v>0.7373997761066123</v>
+        <v>0.7432290381133528</v>
       </c>
       <c r="D221">
-        <v>4.984452159435951</v>
+        <v>4.944639662883481</v>
       </c>
       <c r="E221">
-        <v>6.783265189388199E-07</v>
+        <v>8.305552797054326E-07</v>
       </c>
     </row>
     <row r="222">
@@ -4568,16 +4568,16 @@
         </is>
       </c>
       <c r="B222">
-        <v>-0.5588668861938968</v>
+        <v>-0.5334602240848799</v>
       </c>
       <c r="C222">
-        <v>0.7373997761066095</v>
+        <v>0.7432290381133501</v>
       </c>
       <c r="D222">
-        <v>-0.7578886030378977</v>
+        <v>-0.7177602014031128</v>
       </c>
       <c r="E222">
-        <v>0.448612509843082</v>
+        <v>0.4729941912193025</v>
       </c>
     </row>
     <row r="223">
@@ -4587,16 +4587,16 @@
         </is>
       </c>
       <c r="B223">
-        <v>2.414054531203461</v>
+        <v>2.399460923394698</v>
       </c>
       <c r="C223">
-        <v>0.7886575773549516</v>
+        <v>0.794892040397884</v>
       </c>
       <c r="D223">
-        <v>3.060966635608658</v>
+        <v>3.018599761287892</v>
       </c>
       <c r="E223">
-        <v>0.002237407723622432</v>
+        <v>0.002573545007193429</v>
       </c>
     </row>
     <row r="224">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="B224">
-        <v>6.647367012251975</v>
+        <v>6.668612215967243</v>
       </c>
       <c r="C224">
-        <v>0.7373997761066154</v>
+        <v>0.7432290381133561</v>
       </c>
       <c r="D224">
-        <v>9.01460405554948</v>
+        <v>8.972486103200609</v>
       </c>
       <c r="E224">
-        <v>4.731811704530349E-19</v>
+        <v>6.833781703677592E-19</v>
       </c>
     </row>
     <row r="225">
@@ -4625,16 +4625,16 @@
         </is>
       </c>
       <c r="B225">
-        <v>-1.29256323136136</v>
+        <v>-1.267261654330007</v>
       </c>
       <c r="C225">
-        <v>0.7375705844415267</v>
+        <v>0.7434011967152043</v>
       </c>
       <c r="D225">
-        <v>-1.752460386337211</v>
+        <v>-1.704680675696427</v>
       </c>
       <c r="E225">
-        <v>0.07985742268200231</v>
+        <v>0.08841895420656956</v>
       </c>
     </row>
     <row r="226">
@@ -4644,16 +4644,16 @@
         </is>
       </c>
       <c r="B226">
-        <v>-2.001462094621945</v>
+        <v>-1.978856971107077</v>
       </c>
       <c r="C226">
-        <v>0.7375705844415279</v>
+        <v>0.7434011967152057</v>
       </c>
       <c r="D226">
-        <v>-2.713587196725595</v>
+        <v>-2.661896402441722</v>
       </c>
       <c r="E226">
-        <v>0.006716561977516233</v>
+        <v>0.007836263949771591</v>
       </c>
     </row>
     <row r="227">
@@ -4663,16 +4663,16 @@
         </is>
       </c>
       <c r="B227">
-        <v>-2.664754354159981</v>
+        <v>-2.656864962670051</v>
       </c>
       <c r="C227">
-        <v>0.7373997761066137</v>
+        <v>0.7432290381133542</v>
       </c>
       <c r="D227">
-        <v>-3.613717335567388</v>
+        <v>-3.574759362758964</v>
       </c>
       <c r="E227">
-        <v>0.00030976163668475</v>
+        <v>0.0003593830471547045</v>
       </c>
     </row>
     <row r="228">
@@ -4682,16 +4682,16 @@
         </is>
       </c>
       <c r="B228">
-        <v>-2.285871555304365</v>
+        <v>-2.268643454941294</v>
       </c>
       <c r="C228">
-        <v>0.7375705844415255</v>
+        <v>0.7434011967152031</v>
       </c>
       <c r="D228">
-        <v>-3.099190238226737</v>
+        <v>-3.051708101850704</v>
       </c>
       <c r="E228">
-        <v>0.00196920277072371</v>
+        <v>0.002307224886996551</v>
       </c>
     </row>
     <row r="229">
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="B229">
-        <v>-2.343194736588345</v>
+        <v>-2.338467626143997</v>
       </c>
       <c r="C229">
-        <v>0.737399776106617</v>
+        <v>0.7432290381133575</v>
       </c>
       <c r="D229">
-        <v>-3.177645033959916</v>
+        <v>-3.146362031386794</v>
       </c>
       <c r="E229">
-        <v>0.001508848439926376</v>
+        <v>0.001679004148473571</v>
       </c>
     </row>
     <row r="230">
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="B230">
-        <v>-2.311870569798858</v>
+        <v>-2.31482099724372</v>
       </c>
       <c r="C230">
-        <v>0.7373997761066143</v>
+        <v>0.7432290381133548</v>
       </c>
       <c r="D230">
-        <v>-3.135165814675545</v>
+        <v>-3.114545958968131</v>
       </c>
       <c r="E230">
-        <v>0.001744077531065888</v>
+        <v>0.001870030295925414</v>
       </c>
     </row>
     <row r="231">
@@ -4739,16 +4739,16 @@
         </is>
       </c>
       <c r="B231">
-        <v>-1.835919528332946</v>
+        <v>-1.797048848979367</v>
       </c>
       <c r="C231">
-        <v>0.7401279791382382</v>
+        <v>0.7459788080219892</v>
       </c>
       <c r="D231">
-        <v>-2.480543338559614</v>
+        <v>-2.408981099267897</v>
       </c>
       <c r="E231">
-        <v>0.01320502352012392</v>
+        <v>0.01609259890684381</v>
       </c>
     </row>
     <row r="232">
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="B232">
-        <v>-3.783716849464843</v>
+        <v>-3.783632007743882</v>
       </c>
       <c r="C232">
-        <v>0.740127979138238</v>
+        <v>0.7459788080219892</v>
       </c>
       <c r="D232">
-        <v>-5.112246741260049</v>
+        <v>-5.072036855546105</v>
       </c>
       <c r="E232">
-        <v>3.506525333052379E-07</v>
+        <v>4.322663986814879E-07</v>
       </c>
     </row>
     <row r="233">
@@ -4777,16 +4777,16 @@
         </is>
       </c>
       <c r="B233">
-        <v>-1.663020385377637</v>
+        <v>-1.611000059388639</v>
       </c>
       <c r="C233">
-        <v>0.740127979138239</v>
+        <v>0.7459788080219902</v>
       </c>
       <c r="D233">
-        <v>-2.246936249206467</v>
+        <v>-2.159578854070006</v>
       </c>
       <c r="E233">
-        <v>0.02475951406107458</v>
+        <v>0.03093117683006326</v>
       </c>
     </row>
     <row r="234">
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="B234">
-        <v>-1.408866551866327</v>
+        <v>-1.36506968330495</v>
       </c>
       <c r="C234">
-        <v>0.7373997761066157</v>
+        <v>0.7432290381133563</v>
       </c>
       <c r="D234">
-        <v>-1.910587170645721</v>
+        <v>-1.836674313439232</v>
       </c>
       <c r="E234">
-        <v>0.05620938885963886</v>
+        <v>0.06641553062554478</v>
       </c>
     </row>
     <row r="235">
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B235">
-        <v>-1.593976422079785</v>
+        <v>-1.569740196479993</v>
       </c>
       <c r="C235">
-        <v>0.7373997761066152</v>
+        <v>0.7432290381133558</v>
       </c>
       <c r="D235">
-        <v>-2.161617719082849</v>
+        <v>-2.112054448874453</v>
       </c>
       <c r="E235">
-        <v>0.0307733050711354</v>
+        <v>0.03481315746591369</v>
       </c>
     </row>
     <row r="236">
@@ -4834,16 +4834,16 @@
         </is>
       </c>
       <c r="B236">
-        <v>-0.3214964336736865</v>
+        <v>-0.2861743821592779</v>
       </c>
       <c r="C236">
-        <v>0.7375705844415228</v>
+        <v>0.7434011967152004</v>
       </c>
       <c r="D236">
-        <v>-0.4358856500725536</v>
+        <v>-0.3849528133984323</v>
       </c>
       <c r="E236">
-        <v>0.6629696610354694</v>
+        <v>0.70031585086541</v>
       </c>
     </row>
     <row r="237">
@@ -4853,16 +4853,16 @@
         </is>
       </c>
       <c r="B237">
-        <v>-0.9363526301139846</v>
+        <v>-0.9168203380895042</v>
       </c>
       <c r="C237">
-        <v>0.7375705844415236</v>
+        <v>0.7434011967152012</v>
       </c>
       <c r="D237">
-        <v>-1.269509183074289</v>
+        <v>-1.233277995973876</v>
       </c>
       <c r="E237">
-        <v>0.20441639236825</v>
+        <v>0.2176259939478595</v>
       </c>
     </row>
     <row r="238">
@@ -4872,16 +4872,16 @@
         </is>
       </c>
       <c r="B238">
-        <v>-0.827152603542857</v>
+        <v>-0.7951304293332376</v>
       </c>
       <c r="C238">
-        <v>0.7373997761066156</v>
+        <v>0.7432290381133562</v>
       </c>
       <c r="D238">
-        <v>-1.121715289785042</v>
+        <v>-1.069832297391972</v>
       </c>
       <c r="E238">
-        <v>0.2621265337726593</v>
+        <v>0.2848319170409488</v>
       </c>
     </row>
     <row r="239">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="B239">
-        <v>-1.020931384814775</v>
+        <v>-0.9909706313080918</v>
       </c>
       <c r="C239">
-        <v>0.7375705844415238</v>
+        <v>0.7434011967152014</v>
       </c>
       <c r="D239">
-        <v>-1.384181265292469</v>
+        <v>-1.333022647376414</v>
       </c>
       <c r="E239">
-        <v>0.1664669805156384</v>
+        <v>0.1826856279358977</v>
       </c>
     </row>
     <row r="240">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="B240">
-        <v>0.6435118639946059</v>
+        <v>0.6512034087933014</v>
       </c>
       <c r="C240">
-        <v>0.143697788070253</v>
+        <v>0.1448337418413177</v>
       </c>
       <c r="D240">
-        <v>4.478230824819632</v>
+        <v>4.496213385875031</v>
       </c>
       <c r="E240">
-        <v>7.977642066900546E-06</v>
+        <v>7.33871602586312E-06</v>
       </c>
     </row>
     <row r="241">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B241">
-        <v>0.4834437277009323</v>
+        <v>0.4875427364544759</v>
       </c>
       <c r="C241">
-        <v>0.1438716532940093</v>
+        <v>0.1450089814972015</v>
       </c>
       <c r="D241">
-        <v>3.360243082165669</v>
+        <v>3.362155443205322</v>
       </c>
       <c r="E241">
-        <v>0.0007942903767804701</v>
+        <v>0.0007888424852817334</v>
       </c>
     </row>
     <row r="242">
@@ -4948,16 +4948,16 @@
         </is>
       </c>
       <c r="B242">
-        <v>0.6345123116711637</v>
+        <v>0.6379738403907131</v>
       </c>
       <c r="C242">
-        <v>0.1438716532940089</v>
+        <v>0.1450089814972012</v>
       </c>
       <c r="D242">
-        <v>4.410266352986895</v>
+        <v>4.399547074972227</v>
       </c>
       <c r="E242">
-        <v>1.09073366825162E-05</v>
+        <v>1.145443754509255E-05</v>
       </c>
     </row>
     <row r="243">
@@ -4967,16 +4967,16 @@
         </is>
       </c>
       <c r="B243">
-        <v>1.297795182165532</v>
+        <v>1.305608684080836</v>
       </c>
       <c r="C243">
-        <v>0.143697788070253</v>
+        <v>0.1448337418413178</v>
       </c>
       <c r="D243">
-        <v>9.031420730923477</v>
+        <v>9.01453395791764</v>
       </c>
       <c r="E243">
-        <v>4.084161517218796E-19</v>
+        <v>4.734713345291378E-19</v>
       </c>
     </row>
     <row r="244">
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="B244">
-        <v>1.92802752376203</v>
+        <v>1.937835799781635</v>
       </c>
       <c r="C244">
-        <v>0.1553650870341973</v>
+        <v>0.1565932726512369</v>
       </c>
       <c r="D244">
-        <v>12.40965753997005</v>
+        <v>12.37496200809064</v>
       </c>
       <c r="E244">
-        <v>4.775543138289238E-34</v>
+        <v>7.124912453897143E-34</v>
       </c>
     </row>
     <row r="245">
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="B245">
-        <v>2.650157714766851</v>
+        <v>2.666004045843104</v>
       </c>
       <c r="C245">
-        <v>0.1807855827696802</v>
+        <v>0.1822147214311671</v>
       </c>
       <c r="D245">
-        <v>14.65912089982937</v>
+        <v>14.63111226636101</v>
       </c>
       <c r="E245">
-        <v>3.719040265932216E-46</v>
+        <v>5.383886714991702E-46</v>
       </c>
     </row>
     <row r="246">
@@ -5024,16 +5024,16 @@
         </is>
       </c>
       <c r="B246">
-        <v>3.560802198879052</v>
+        <v>3.583337731752209</v>
       </c>
       <c r="C246">
-        <v>0.1807855827696801</v>
+        <v>0.182214721431167</v>
       </c>
       <c r="D246">
-        <v>19.6962730342026</v>
+        <v>19.66546777125163</v>
       </c>
       <c r="E246">
-        <v>1.123159754403571E-78</v>
+        <v>1.859440219750475E-78</v>
       </c>
     </row>
     <row r="247">
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="B247">
-        <v>4.386230769684707</v>
+        <v>4.422029626801115</v>
       </c>
       <c r="C247">
-        <v>0.1814456305151081</v>
+        <v>0.1828799869585495</v>
       </c>
       <c r="D247">
-        <v>24.1738021314296</v>
+        <v>24.17995375187437</v>
       </c>
       <c r="E247">
-        <v>1.145626613329053E-112</v>
+        <v>1.022512478534082E-112</v>
       </c>
     </row>
   </sheetData>
